--- a/database/event/2034/event_2034_evp_summary.xlsx
+++ b/database/event/2034/event_2034_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.5336</v>
       </c>
       <c r="D2" t="n">
-        <v>3.04</v>
+        <v>2.9697</v>
       </c>
       <c r="E2" t="n">
         <v>8.568199999999999</v>
@@ -548,7 +548,7 @@
         <v>1.5499</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6961</v>
+        <v>1.6443</v>
       </c>
       <c r="E3" t="n">
         <v>5.2416</v>
@@ -594,7 +594,7 @@
         <v>1.2894</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3402</v>
+        <v>1.2934</v>
       </c>
       <c r="E4" t="n">
         <v>4.3606</v>
@@ -640,7 +640,7 @@
         <v>1.0421</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0023</v>
+        <v>0.9601</v>
       </c>
       <c r="E5" t="n">
         <v>3.524</v>
@@ -686,7 +686,7 @@
         <v>1.0221</v>
       </c>
       <c r="D6" t="n">
-        <v>0.975</v>
+        <v>0.9332</v>
       </c>
       <c r="E6" t="n">
         <v>3.4565</v>
@@ -732,7 +732,7 @@
         <v>0.8915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7966</v>
+        <v>0.7573</v>
       </c>
       <c r="E7" t="n">
         <v>3.015</v>
@@ -778,7 +778,7 @@
         <v>0.83</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7125</v>
+        <v>0.6743</v>
       </c>
       <c r="E8" t="n">
         <v>2.8068</v>
@@ -824,7 +824,7 @@
         <v>0.774</v>
       </c>
       <c r="D9" t="n">
-        <v>0.636</v>
+        <v>0.5989</v>
       </c>
       <c r="E9" t="n">
         <v>2.6175</v>
@@ -870,7 +870,7 @@
         <v>0.572</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3601</v>
+        <v>0.3268</v>
       </c>
       <c r="E10" t="n">
         <v>1.9345</v>
@@ -916,7 +916,7 @@
         <v>0.5605</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3443</v>
+        <v>0.3112</v>
       </c>
       <c r="E11" t="n">
         <v>1.8954</v>
@@ -962,7 +962,7 @@
         <v>0.473</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2248</v>
+        <v>0.1934</v>
       </c>
       <c r="E12" t="n">
         <v>1.5996</v>
@@ -1008,7 +1008,7 @@
         <v>0.431</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1675</v>
+        <v>0.1368</v>
       </c>
       <c r="E13" t="n">
         <v>1.4577</v>
@@ -1054,7 +1054,7 @@
         <v>0.3275</v>
       </c>
       <c r="D14" t="n">
-        <v>0.026</v>
+        <v>-0.0027</v>
       </c>
       <c r="E14" t="n">
         <v>1.1075</v>
@@ -1100,7 +1100,7 @@
         <v>0.2851</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0319</v>
+        <v>-0.0598</v>
       </c>
       <c r="E15" t="n">
         <v>0.9641</v>
@@ -1146,7 +1146,7 @@
         <v>0.2263</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1122</v>
+        <v>-0.1391</v>
       </c>
       <c r="E16" t="n">
         <v>0.7652</v>
@@ -1192,7 +1192,7 @@
         <v>0.2217</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1185</v>
+        <v>-0.1452</v>
       </c>
       <c r="E17" t="n">
         <v>0.7498</v>
@@ -1238,7 +1238,7 @@
         <v>0.216</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1263</v>
+        <v>-0.153</v>
       </c>
       <c r="E18" t="n">
         <v>0.7302999999999999</v>
@@ -1284,7 +1284,7 @@
         <v>0.1218</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.255</v>
+        <v>-0.2798</v>
       </c>
       <c r="E19" t="n">
         <v>0.4118</v>
@@ -1330,7 +1330,7 @@
         <v>0.1032</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2804</v>
+        <v>-0.3049</v>
       </c>
       <c r="E20" t="n">
         <v>0.3489</v>
@@ -1376,7 +1376,7 @@
         <v>0.0885</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3005</v>
+        <v>-0.3247</v>
       </c>
       <c r="E21" t="n">
         <v>0.2992</v>
@@ -1422,7 +1422,7 @@
         <v>0.0765</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3169</v>
+        <v>-0.3409</v>
       </c>
       <c r="E22" t="n">
         <v>0.2586</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0078</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.432</v>
+        <v>-0.4544</v>
       </c>
       <c r="E23" t="n">
         <v>-0.0264</v>
@@ -1514,7 +1514,7 @@
         <v>-0.068</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5142</v>
+        <v>-0.5355</v>
       </c>
       <c r="E24" t="n">
         <v>-0.2298</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0977</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5548</v>
+        <v>-0.5755</v>
       </c>
       <c r="E25" t="n">
         <v>-0.3303</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1323</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6021</v>
+        <v>-0.6222</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4475</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1881</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6783</v>
+        <v>-0.6973</v>
       </c>
       <c r="E27" t="n">
         <v>-0.6361</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1937</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.7049</v>
       </c>
       <c r="E28" t="n">
         <v>-0.6551</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1963</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6895</v>
+        <v>-0.7084</v>
       </c>
       <c r="E29" t="n">
         <v>-0.6637999999999999</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2138</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7134</v>
+        <v>-0.732</v>
       </c>
       <c r="E30" t="n">
         <v>-0.723</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2212</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7236</v>
+        <v>-0.742</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7482</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2733</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7947</v>
+        <v>-0.8121</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9242</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2849</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8106</v>
+        <v>-0.8277</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9634</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2957</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E34" t="n">
         <v>-1</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2957</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E35" t="n">
         <v>-1</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2957</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E36" t="n">
         <v>-1</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2957</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E37" t="n">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3028</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.835</v>
+        <v>-0.8518</v>
       </c>
       <c r="E38" t="n">
         <v>-1.0239</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4733</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.068</v>
+        <v>-1.0816</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6007</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4939</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0961</v>
+        <v>-1.1093</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6702</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5477</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1696</v>
+        <v>-1.1818</v>
       </c>
       <c r="E41" t="n">
         <v>-1.8521</v>

--- a/database/event/2034/event_2034_evp_summary.xlsx
+++ b/database/event/2034/event_2034_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.568199999999999</v>
+        <v>7.7932</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5336</v>
+        <v>2.3045</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9697</v>
+        <v>2.8802</v>
       </c>
       <c r="E2" t="n">
-        <v>8.568199999999999</v>
+        <v>7.7932</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4835</v>
+        <v>2.7805</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0847</v>
+        <v>5.0127</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4835</v>
+        <v>4.3106</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0129</v>
+        <v>2.2413</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0847</v>
+        <v>5.0127</v>
       </c>
       <c r="K2" t="n">
         <v>73</v>
@@ -529,7 +529,7 @@
         <v>132</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0976</v>
+        <v>7.254</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2416</v>
+        <v>5.6305</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5499</v>
+        <v>1.6649</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6443</v>
+        <v>1.9039</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2416</v>
+        <v>5.6305</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1455</v>
+        <v>2.5786</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0961</v>
+        <v>3.0519</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1455</v>
+        <v>3.5992</v>
       </c>
       <c r="I3" t="n">
-        <v>1.739</v>
+        <v>1.8714</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0961</v>
+        <v>3.0519</v>
       </c>
       <c r="K3" t="n">
         <v>73</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8351</v>
+        <v>4.923299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3606</v>
+        <v>4.2989</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2894</v>
+        <v>1.2712</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2934</v>
+        <v>1.3027</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3606</v>
+        <v>4.2989</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7018</v>
+        <v>2.9425</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6588</v>
+        <v>1.3564</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7018</v>
+        <v>4.8814</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1899</v>
+        <v>2.5381</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6588</v>
+        <v>1.3564</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -621,7 +621,7 @@
         <v>118</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8487</v>
+        <v>3.8945</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.524</v>
+        <v>3.7852</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0421</v>
+        <v>1.1193</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9601</v>
+        <v>1.0708</v>
       </c>
       <c r="E5" t="n">
-        <v>3.524</v>
+        <v>3.7852</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8822</v>
+        <v>2.0775</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6417</v>
+        <v>1.7077</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8822</v>
+        <v>2.0775</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5256</v>
+        <v>1.0802</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6417</v>
+        <v>1.7077</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L5" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1673</v>
+        <v>2.7879</v>
       </c>
       <c r="N5" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4565</v>
+        <v>3.6404</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0221</v>
+        <v>1.0765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9332</v>
+        <v>1.0054</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4565</v>
+        <v>3.6404</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1956</v>
+        <v>2.5424</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2609</v>
+        <v>1.098</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1956</v>
+        <v>3.4717</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7796</v>
+        <v>1.8051</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2609</v>
+        <v>1.098</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -713,7 +713,7 @@
         <v>118</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0405</v>
+        <v>2.9031</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.015</v>
+        <v>3.6066</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8915</v>
+        <v>1.0665</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7573</v>
+        <v>0.9902</v>
       </c>
       <c r="E7" t="n">
-        <v>3.015</v>
+        <v>3.6066</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1697</v>
+        <v>2.3106</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8453000000000001</v>
+        <v>1.296</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1697</v>
+        <v>2.6547</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7586</v>
+        <v>1.3803</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8453000000000001</v>
+        <v>1.296</v>
       </c>
       <c r="K7" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6039</v>
+        <v>2.6763</v>
       </c>
       <c r="N7" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8068</v>
+        <v>3.4241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.83</v>
+        <v>1.0125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6743</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8068</v>
+        <v>3.4241</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6449</v>
+        <v>2.5828</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1619</v>
+        <v>0.8413</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6449</v>
+        <v>3.6138</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3332</v>
+        <v>1.879</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1619</v>
+        <v>0.8413</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4951</v>
+        <v>2.7203</v>
       </c>
       <c r="N8" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6175</v>
+        <v>3.3559</v>
       </c>
       <c r="C9" t="n">
-        <v>0.774</v>
+        <v>0.9923</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5989</v>
+        <v>0.877</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6175</v>
+        <v>3.3559</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9801</v>
+        <v>2.3894</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6374</v>
+        <v>0.9665</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9801</v>
+        <v>2.9326</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7944</v>
+        <v>1.5248</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6374</v>
+        <v>0.9665</v>
       </c>
       <c r="K9" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4318</v>
+        <v>2.4913</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9345</v>
+        <v>2.8325</v>
       </c>
       <c r="C10" t="n">
-        <v>0.572</v>
+        <v>0.8376</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3268</v>
+        <v>0.6407</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9345</v>
+        <v>2.8325</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3678</v>
+        <v>1.397</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3023</v>
+        <v>1.4355</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3678</v>
+        <v>1.397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2981</v>
+        <v>0.7264</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3023</v>
+        <v>1.4355</v>
       </c>
       <c r="K10" t="n">
         <v>73</v>
@@ -897,7 +897,7 @@
         <v>132</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0042</v>
+        <v>2.1619</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8954</v>
+        <v>2.4472</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5605</v>
+        <v>0.7236</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3112</v>
+        <v>0.4668</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8954</v>
+        <v>2.4472</v>
       </c>
       <c r="F11" t="n">
-        <v>0.747</v>
+        <v>1.6138</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1484</v>
+        <v>0.8334</v>
       </c>
       <c r="H11" t="n">
-        <v>0.747</v>
+        <v>1.6138</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6055</v>
+        <v>0.8391</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1484</v>
+        <v>0.8334</v>
       </c>
       <c r="K11" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7539</v>
+        <v>1.6725</v>
       </c>
       <c r="N11" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5996</v>
+        <v>2.079</v>
       </c>
       <c r="C12" t="n">
-        <v>0.473</v>
+        <v>0.6148</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1934</v>
+        <v>0.3006</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5996</v>
+        <v>2.079</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3909</v>
+        <v>2.6546</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7913</v>
+        <v>-0.5756</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3909</v>
+        <v>3.8667</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9379</v>
+        <v>2.0105</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7913</v>
+        <v>-0.5756</v>
       </c>
       <c r="K12" t="n">
         <v>89</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1466</v>
+        <v>1.4349</v>
       </c>
       <c r="N12" t="n">
         <v>133</v>
@@ -998,124 +998,124 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4577</v>
+        <v>2.0257</v>
       </c>
       <c r="C13" t="n">
-        <v>0.431</v>
+        <v>0.599</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1368</v>
+        <v>0.2765</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4577</v>
+        <v>2.0257</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7821</v>
+        <v>-0.4087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6756</v>
+        <v>2.4344</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7821</v>
+        <v>-0.4087</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6339</v>
+        <v>-0.2125</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6756</v>
+        <v>2.4344</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L13" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3095</v>
+        <v>2.2219</v>
       </c>
       <c r="N13" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1075</v>
+        <v>1.7139</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3275</v>
+        <v>0.5068</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0027</v>
+        <v>0.1357</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1075</v>
+        <v>1.7139</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1075</v>
+        <v>2.0883</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.3744</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1075</v>
+        <v>2.0883</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1075</v>
+        <v>1.0858</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3744</v>
       </c>
       <c r="K14" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1075</v>
+        <v>0.7114</v>
       </c>
       <c r="N14" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2851</v>
+        <v>0.3318</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0598</v>
+        <v>-0.1315</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9641</v>
+        <v>1.122</v>
       </c>
       <c r="N15" t="n">
         <v>89</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2263</v>
+        <v>0.3203</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1391</v>
+        <v>-0.149</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7652</v>
+        <v>1.0832</v>
       </c>
       <c r="N16" t="n">
         <v>89</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7498</v>
+        <v>1.0204</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2217</v>
+        <v>0.3017</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1452</v>
+        <v>-0.1774</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7498</v>
+        <v>1.0204</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7498</v>
+        <v>1.333</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.3126</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7498</v>
+        <v>1.333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7498</v>
+        <v>0.6931</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.3126</v>
       </c>
       <c r="K17" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7498</v>
+        <v>0.3805000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.0046</v>
       </c>
       <c r="C18" t="n">
-        <v>0.216</v>
+        <v>0.2971</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.153</v>
+        <v>-0.1845</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.0046</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2734</v>
+        <v>1.3368</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5431</v>
+        <v>-0.3322</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2734</v>
+        <v>1.3368</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0321</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5431</v>
+        <v>-0.3322</v>
       </c>
       <c r="K18" t="n">
         <v>54</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>0.489</v>
+        <v>0.3629000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>112</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emagine</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1218</v>
+        <v>0.2318</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2798</v>
+        <v>-0.2841</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4118</v>
+        <v>0.7839</v>
       </c>
       <c r="N19" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3489</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1032</v>
+        <v>0.2201</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3049</v>
+        <v>-0.3019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3489</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7847</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4358</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7847</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.636</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4358</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="L20" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2002</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>emagine</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2992</v>
+        <v>0.6751</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0885</v>
+        <v>0.1996</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3247</v>
+        <v>-0.3332</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2992</v>
+        <v>0.6751</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7701</v>
+        <v>0.6751</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4709</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7701</v>
+        <v>0.6751</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6242</v>
+        <v>0.6751</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4709</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1533</v>
+        <v>0.6751</v>
       </c>
       <c r="N21" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0765</v>
+        <v>0.1782</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3409</v>
+        <v>-0.366</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2586</v>
+        <v>0.6025</v>
       </c>
       <c r="N22" t="n">
         <v>73</v>
@@ -1458,231 +1458,231 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zewsy</t>
+          <t>just9n</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0264</v>
+        <v>0.3875</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0078</v>
+        <v>0.1146</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4631</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0264</v>
+        <v>0.3875</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0264</v>
+        <v>0.5802</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.1927</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0264</v>
+        <v>0.5802</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0264</v>
+        <v>0.3017</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.1927</v>
       </c>
       <c r="K23" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0264</v>
+        <v>0.109</v>
       </c>
       <c r="N23" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>just9n</t>
+          <t>zewsy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2298</v>
+        <v>-0.0397</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.068</v>
+        <v>-0.0117</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5355</v>
+        <v>-0.6559</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2298</v>
+        <v>-0.0397</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0659</v>
+        <v>-0.0397</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2957</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0659</v>
+        <v>-0.0397</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0534</v>
+        <v>-0.0397</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2957</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2423</v>
+        <v>-0.0397</v>
       </c>
       <c r="N24" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MoeycQ</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0977</v>
+        <v>-0.0328</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5755</v>
+        <v>-0.6881</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3303</v>
+        <v>-0.111</v>
       </c>
       <c r="N25" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>MoeycQ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1323</v>
+        <v>-0.0415</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6222</v>
+        <v>-0.7014</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4475</v>
+        <v>-0.1405</v>
       </c>
       <c r="N26" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1881</v>
+        <v>-0.1064</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6973</v>
+        <v>-0.8004</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6361</v>
+        <v>-0.3598</v>
       </c>
       <c r="N27" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1937</v>
+        <v>-0.1181</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7049</v>
+        <v>-0.8184</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6551</v>
+        <v>-0.3995</v>
       </c>
       <c r="N28" t="n">
         <v>89</v>
@@ -1734,78 +1734,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>decent</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1963</v>
+        <v>-0.1312</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7084</v>
+        <v>-0.8384</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4438</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>malle</t>
+          <t>decent</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2138</v>
+        <v>-0.1492</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.732</v>
+        <v>-0.8659</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.723</v>
+        <v>-0.5047</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
@@ -1826,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>malle</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2212</v>
+        <v>-0.1538</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.742</v>
+        <v>-0.8728</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7482</v>
+        <v>-0.52</v>
       </c>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>darti</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2733</v>
+        <v>-0.1856</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8121</v>
+        <v>-0.9214</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9242</v>
+        <v>-0.6278</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>darti</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2849</v>
+        <v>-0.199</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8277</v>
+        <v>-0.9418</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9634</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>downie</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1</v>
+        <v>-0.7366</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2957</v>
+        <v>-0.2178</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8423</v>
+        <v>-0.9706</v>
       </c>
       <c r="E34" t="n">
-        <v>-1</v>
+        <v>-0.7366</v>
       </c>
       <c r="F34" t="n">
-        <v>-1</v>
+        <v>0.2073</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>0.2073</v>
       </c>
       <c r="I34" t="n">
-        <v>-1</v>
+        <v>0.1078</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>-0.8361</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>downie</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2957</v>
+        <v>-0.2226</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8423</v>
+        <v>-0.9779</v>
       </c>
       <c r="E35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="I35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-0.7528</v>
       </c>
       <c r="N35" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2957</v>
+        <v>-0.2244</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8423</v>
+        <v>-0.9807</v>
       </c>
       <c r="E36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="I36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-0.759</v>
       </c>
       <c r="N36" t="n">
         <v>73</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>atter</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2957</v>
+        <v>-0.2265</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8423</v>
+        <v>-0.9839</v>
       </c>
       <c r="E37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="I37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-0.7661</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>atter</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0239</v>
+        <v>-0.9627</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3028</v>
+        <v>-0.2847</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8518</v>
+        <v>-1.0726</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0239</v>
+        <v>-0.9627</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0239</v>
+        <v>-0.9627</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0239</v>
+        <v>-0.9627</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0194</v>
+        <v>-0.9627</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L38" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0194</v>
+        <v>-0.9627</v>
       </c>
       <c r="N38" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6007</v>
+        <v>-1.2261</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4733</v>
+        <v>-0.3626</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0816</v>
+        <v>-1.1915</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6007</v>
+        <v>-1.2261</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7299</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8708</v>
+        <v>-0.6359</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7299</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5916</v>
+        <v>-0.3069</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8708</v>
+        <v>-0.6359</v>
       </c>
       <c r="K39" t="n">
         <v>89</v>
@@ -2231,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4624</v>
+        <v>-0.9428000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>133</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6702</v>
+        <v>-1.2432</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4939</v>
+        <v>-0.3676</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1093</v>
+        <v>-1.1993</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6702</v>
+        <v>-1.2432</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6702</v>
+        <v>-0.4439</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.7993</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6702</v>
+        <v>-0.4439</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5432</v>
+        <v>-0.2308</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.7993</v>
       </c>
       <c r="K40" t="n">
         <v>89</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5432</v>
+        <v>-1.0301</v>
       </c>
       <c r="N40" t="n">
         <v>133</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8521</v>
+        <v>-1.8953</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5477</v>
+        <v>-0.5604</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1818</v>
+        <v>-1.4936</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8521</v>
+        <v>-1.8953</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8814</v>
+        <v>-1.1966</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9707</v>
+        <v>-0.6987</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8814</v>
+        <v>-1.1966</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7144</v>
+        <v>-0.6222</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9707</v>
+        <v>-0.6987</v>
       </c>
       <c r="K41" t="n">
         <v>89</v>
@@ -2323,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6851</v>
+        <v>-1.3209</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6131</v>
+        <v>1.4015</v>
       </c>
       <c r="J2" t="n">
-        <v>40.3275</v>
+        <v>35.0375</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0301</v>
+        <v>1.0305</v>
       </c>
       <c r="J3" t="n">
-        <v>25.7525</v>
+        <v>25.7625</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5334</v>
+        <v>0.6148</v>
       </c>
       <c r="J4" t="n">
-        <v>13.335</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2777</v>
+        <v>0.3628</v>
       </c>
       <c r="J5" t="n">
-        <v>6.9425</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3245</v>
+        <v>-0.2402</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.112500000000001</v>
+        <v>-6.005</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2618</v>
+        <v>0.2655</v>
       </c>
       <c r="J7" t="n">
-        <v>6.545</v>
+        <v>6.6375</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0024</v>
+        <v>-0.0276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.77</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3729</v>
+        <v>-0.2467</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.3225</v>
+        <v>-6.1675</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4779</v>
+        <v>-0.3139</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.9475</v>
+        <v>-7.8475</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6136</v>
+        <v>-0.4081</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.34</v>
+        <v>-10.2025</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5596</v>
+        <v>0.5125</v>
       </c>
       <c r="J12" t="n">
-        <v>15.6688</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4679</v>
+        <v>0.419</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1012</v>
+        <v>11.732</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.89</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2442</v>
+        <v>-0.145</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.8376</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4116</v>
+        <v>-0.2587</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.5248</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4803</v>
+        <v>-0.3074</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.4484</v>
+        <v>-8.607200000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4343</v>
+        <v>0.3728</v>
       </c>
       <c r="J17" t="n">
-        <v>12.1604</v>
+        <v>10.4384</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4205</v>
+        <v>0.3608</v>
       </c>
       <c r="J18" t="n">
-        <v>11.774</v>
+        <v>10.1024</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3488</v>
+        <v>0.2999</v>
       </c>
       <c r="J19" t="n">
-        <v>9.766400000000001</v>
+        <v>8.3972</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0445</v>
+        <v>0.0675</v>
       </c>
       <c r="J20" t="n">
-        <v>1.246</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2297</v>
+        <v>-0.1266</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.4316</v>
+        <v>-3.5448</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6973</v>
+        <v>1.4664</v>
       </c>
       <c r="J22" t="n">
-        <v>35.6433</v>
+        <v>30.7944</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0816</v>
+        <v>1.0957</v>
       </c>
       <c r="J23" t="n">
-        <v>22.7136</v>
+        <v>23.0097</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0022</v>
+        <v>1.0609</v>
       </c>
       <c r="J24" t="n">
-        <v>21.0462</v>
+        <v>22.2789</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7526</v>
+        <v>0.8746</v>
       </c>
       <c r="J25" t="n">
-        <v>15.8046</v>
+        <v>18.3666</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.22</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4401</v>
+        <v>0.5536</v>
       </c>
       <c r="J26" t="n">
-        <v>9.242100000000001</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.72</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2973</v>
+        <v>-0.2513</v>
       </c>
       <c r="J27" t="n">
-        <v>-6.2433</v>
+        <v>-5.2773</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.71</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3127</v>
+        <v>-0.2619</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.5667</v>
+        <v>-5.4999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.52</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6382</v>
+        <v>-0.442</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.4022</v>
+        <v>-9.282</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.48</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6977</v>
+        <v>-0.4795</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.6517</v>
+        <v>-10.0695</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7262</v>
+        <v>-0.4984</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.2502</v>
+        <v>-10.4664</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4225</v>
+        <v>1.0308</v>
       </c>
       <c r="J32" t="n">
-        <v>27.0275</v>
+        <v>19.5852</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.67</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3841</v>
+        <v>1.0082</v>
       </c>
       <c r="J33" t="n">
-        <v>26.2979</v>
+        <v>19.1558</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.65</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3449</v>
+        <v>0.9856</v>
       </c>
       <c r="J34" t="n">
-        <v>25.5531</v>
+        <v>18.7264</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.48</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.7913</v>
       </c>
       <c r="J35" t="n">
-        <v>18.4167</v>
+        <v>15.0347</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.34</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6774</v>
+        <v>0.6162</v>
       </c>
       <c r="J36" t="n">
-        <v>12.8706</v>
+        <v>11.7078</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.63</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3843</v>
+        <v>-0.3181</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.3017</v>
+        <v>-6.0439</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.55</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5102</v>
+        <v>-0.3999</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.6938</v>
+        <v>-7.5981</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.54</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5268</v>
+        <v>-0.4096</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.0092</v>
+        <v>-7.7824</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.45</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.701</v>
+        <v>-0.4908</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.319</v>
+        <v>-9.325200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8902</v>
+        <v>-0.6179</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.9138</v>
+        <v>-11.7401</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0442</v>
+        <v>0.7695</v>
       </c>
       <c r="J42" t="n">
-        <v>26.105</v>
+        <v>19.2375</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9574</v>
+        <v>0.719</v>
       </c>
       <c r="J43" t="n">
-        <v>23.935</v>
+        <v>17.975</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9351</v>
+        <v>0.7063</v>
       </c>
       <c r="J44" t="n">
-        <v>23.3775</v>
+        <v>17.6575</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.3</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7036</v>
+        <v>0.592</v>
       </c>
       <c r="J45" t="n">
-        <v>17.59</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0597</v>
+        <v>0.0209</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.4925</v>
+        <v>0.5225</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2145</v>
+        <v>0.2072</v>
       </c>
       <c r="J47" t="n">
-        <v>5.3625</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.2575</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2676</v>
+        <v>-0.1814</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.69</v>
+        <v>-4.535</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4439</v>
+        <v>-0.2891</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.0975</v>
+        <v>-7.2275</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4865</v>
+        <v>-0.3178</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.1625</v>
+        <v>-7.945</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3905</v>
+        <v>0.3955</v>
       </c>
       <c r="J52" t="n">
-        <v>11.715</v>
+        <v>11.865</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1141</v>
+        <v>-0.0911</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.423</v>
+        <v>-2.733</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2023</v>
+        <v>-0.1347</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.069</v>
+        <v>-4.041</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.222</v>
+        <v>-0.1452</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.66</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.62</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6042</v>
+        <v>-0.3994</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.126</v>
+        <v>-11.982</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2788</v>
+        <v>0.9045</v>
       </c>
       <c r="J57" t="n">
-        <v>38.364</v>
+        <v>27.135</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.517</v>
+        <v>0.4669</v>
       </c>
       <c r="J58" t="n">
-        <v>15.51</v>
+        <v>14.007</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4868</v>
+        <v>0.4529</v>
       </c>
       <c r="J59" t="n">
-        <v>14.604</v>
+        <v>13.587</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3464</v>
+        <v>0.3787</v>
       </c>
       <c r="J60" t="n">
-        <v>10.392</v>
+        <v>11.361</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.263</v>
+        <v>-0.1835</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.89</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4548</v>
+        <v>0.4458</v>
       </c>
       <c r="J62" t="n">
-        <v>12.7344</v>
+        <v>12.4824</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2138</v>
+        <v>-0.1674</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.9864</v>
+        <v>-4.6872</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2686</v>
+        <v>-0.1975</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.5208</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.429</v>
+        <v>-0.2833</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.012</v>
+        <v>-7.9324</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7967</v>
+        <v>-0.5445</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.3076</v>
+        <v>-15.246</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9638</v>
+        <v>0.7278</v>
       </c>
       <c r="J67" t="n">
-        <v>26.9864</v>
+        <v>20.3784</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8212</v>
+        <v>0.6526</v>
       </c>
       <c r="J68" t="n">
-        <v>22.9936</v>
+        <v>18.2728</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8212</v>
+        <v>0.6526</v>
       </c>
       <c r="J69" t="n">
-        <v>22.9936</v>
+        <v>18.2728</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.34</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7927</v>
+        <v>0.6403</v>
       </c>
       <c r="J70" t="n">
-        <v>22.1956</v>
+        <v>17.9284</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.24</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5369</v>
+        <v>0.5084</v>
       </c>
       <c r="J71" t="n">
-        <v>15.0332</v>
+        <v>14.2352</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5091</v>
+        <v>0.5997</v>
       </c>
       <c r="J72" t="n">
-        <v>14.7639</v>
+        <v>17.3913</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.325</v>
+        <v>0.3587</v>
       </c>
       <c r="J73" t="n">
-        <v>9.425000000000001</v>
+        <v>10.4023</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.01</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0636</v>
+        <v>0.0456</v>
       </c>
       <c r="J74" t="n">
-        <v>1.8444</v>
+        <v>1.3224</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5118</v>
+        <v>-0.3311</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.8422</v>
+        <v>-9.601900000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.64</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5893</v>
+        <v>-0.3875</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.0897</v>
+        <v>-11.2375</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5017</v>
+        <v>1.3229</v>
       </c>
       <c r="J77" t="n">
-        <v>43.5493</v>
+        <v>38.3641</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1301</v>
+        <v>0.1748</v>
       </c>
       <c r="J78" t="n">
-        <v>3.7729</v>
+        <v>5.0692</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1301</v>
+        <v>0.1748</v>
       </c>
       <c r="J79" t="n">
-        <v>3.7729</v>
+        <v>5.0692</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3573</v>
+        <v>-0.2898</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.3617</v>
+        <v>-8.404199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4734</v>
+        <v>-0.4082</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.7286</v>
+        <v>-11.8378</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.19</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3375</v>
+        <v>1.1556</v>
       </c>
       <c r="J82" t="n">
-        <v>25.4125</v>
+        <v>21.9564</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6965</v>
+        <v>0.6394</v>
       </c>
       <c r="J83" t="n">
-        <v>13.2335</v>
+        <v>12.1486</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.29</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3533</v>
+        <v>0.3658</v>
       </c>
       <c r="J84" t="n">
-        <v>6.7127</v>
+        <v>6.9502</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3272</v>
+        <v>0.3426</v>
       </c>
       <c r="J85" t="n">
-        <v>6.2168</v>
+        <v>6.5094</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3777</v>
+        <v>-0.228</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.1763</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0294</v>
+        <v>-0.0146</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5586</v>
+        <v>-0.2774</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.91</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0645</v>
+        <v>-0.0801</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.2255</v>
+        <v>-1.5219</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5246</v>
+        <v>-0.3545</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.9674</v>
+        <v>-6.7355</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6372</v>
+        <v>-0.4292</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.1068</v>
+        <v>-8.1548</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7033</v>
+        <v>-0.476</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.3627</v>
+        <v>-9.044</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.11</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2818</v>
+        <v>0.2975</v>
       </c>
       <c r="J92" t="n">
-        <v>11.5538</v>
+        <v>12.1975</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="J93" t="n">
-        <v>3.5629</v>
+        <v>2.4354</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2415</v>
+        <v>-0.1559</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.9015</v>
+        <v>-6.3919</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.341</v>
+        <v>-0.2171</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.981</v>
+        <v>-8.9011</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4861</v>
+        <v>-0.3149</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.9301</v>
+        <v>-12.9109</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>1.114</v>
+        <v>1.0675</v>
       </c>
       <c r="J97" t="n">
-        <v>45.674</v>
+        <v>43.7675</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7839</v>
+        <v>0.7677</v>
       </c>
       <c r="J98" t="n">
-        <v>32.1399</v>
+        <v>31.4757</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0361</v>
+        <v>0.0236</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.4801</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1971</v>
+        <v>-0.1272</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.081099999999999</v>
+        <v>-5.2152</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2704</v>
+        <v>-0.1994</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.0864</v>
+        <v>-8.1754</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.6767</v>
+        <v>1.4446</v>
       </c>
       <c r="J102" t="n">
-        <v>36.8874</v>
+        <v>31.7812</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7282</v>
+        <v>0.793</v>
       </c>
       <c r="J103" t="n">
-        <v>16.0204</v>
+        <v>17.446</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.623</v>
+        <v>0.7043</v>
       </c>
       <c r="J104" t="n">
-        <v>13.706</v>
+        <v>15.4946</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.271</v>
+        <v>0.3587</v>
       </c>
       <c r="J105" t="n">
-        <v>5.962</v>
+        <v>7.8914</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1618</v>
+        <v>0.2471</v>
       </c>
       <c r="J106" t="n">
-        <v>3.5596</v>
+        <v>5.4362</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.91</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0588</v>
+        <v>-0.0767</v>
       </c>
       <c r="J107" t="n">
-        <v>-1.2936</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.82</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2092</v>
+        <v>-0.1798</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.6024</v>
+        <v>-3.9556</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.67</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4721</v>
+        <v>-0.3248</v>
       </c>
       <c r="J109" t="n">
-        <v>-10.3862</v>
+        <v>-7.1456</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4882</v>
+        <v>-0.3341</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.7404</v>
+        <v>-7.3502</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7642</v>
+        <v>-0.5208</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.8124</v>
+        <v>-11.4576</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>2.25</v>
       </c>
       <c r="I112" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J112" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.81</v>
       </c>
       <c r="I113" t="n">
-        <v>1.6604</v>
+        <v>1.4464</v>
       </c>
       <c r="J113" t="n">
-        <v>29.8872</v>
+        <v>26.0352</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.605</v>
+        <v>0.7318</v>
       </c>
       <c r="J114" t="n">
-        <v>10.89</v>
+        <v>13.1724</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.24</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4721</v>
+        <v>0.592</v>
       </c>
       <c r="J115" t="n">
-        <v>8.4978</v>
+        <v>10.656</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1503</v>
+        <v>-0.0643</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.7054</v>
+        <v>-1.1574</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0412</v>
+        <v>0.0008</v>
       </c>
       <c r="J117" t="n">
-        <v>0.7416</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.53</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.605</v>
+        <v>-0.428</v>
       </c>
       <c r="J118" t="n">
-        <v>-10.89</v>
+        <v>-7.704</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.53</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.605</v>
+        <v>-0.428</v>
       </c>
       <c r="J119" t="n">
-        <v>-10.89</v>
+        <v>-7.704</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.715</v>
+        <v>-0.4931</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.87</v>
+        <v>-8.8758</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9054</v>
+        <v>-0.6286</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.2972</v>
+        <v>-11.3148</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4391</v>
+        <v>1.2812</v>
       </c>
       <c r="J122" t="n">
-        <v>37.4166</v>
+        <v>33.3112</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9301</v>
+        <v>0.9218</v>
       </c>
       <c r="J123" t="n">
-        <v>24.1826</v>
+        <v>23.9668</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6223</v>
+        <v>0.6166</v>
       </c>
       <c r="J124" t="n">
-        <v>16.1798</v>
+        <v>16.0316</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1649</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.2874</v>
+        <v>-2.3998</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.1156</v>
+        <v>-1.1057</v>
       </c>
       <c r="J126" t="n">
-        <v>-29.0056</v>
+        <v>-28.7482</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2233</v>
+        <v>0.2208</v>
       </c>
       <c r="J127" t="n">
-        <v>5.8058</v>
+        <v>5.7408</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.1346</v>
+        <v>-1.9786</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1595</v>
+        <v>-0.1223</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.147</v>
+        <v>-3.1798</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3471</v>
+        <v>-0.2239</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.0246</v>
+        <v>-5.8214</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3495</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.8788</v>
+        <v>-9.087</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3048</v>
+        <v>0.2489</v>
       </c>
       <c r="J132" t="n">
-        <v>7.62</v>
+        <v>6.2225</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.07</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2202</v>
+        <v>0.1666</v>
       </c>
       <c r="J133" t="n">
-        <v>5.505</v>
+        <v>4.165</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2107</v>
+        <v>-0.1439</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.2675</v>
+        <v>-3.5975</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5089</v>
+        <v>-0.3316</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.7225</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.66</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.549</v>
+        <v>-0.36</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.725</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8828</v>
+        <v>0.7998</v>
       </c>
       <c r="J137" t="n">
-        <v>22.07</v>
+        <v>19.995</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.61</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8183</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>20.4575</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.155</v>
+        <v>-0.0725</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.875</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.155</v>
+        <v>-0.0725</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.875</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.91</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.262</v>
+        <v>-0.1465</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.55</v>
+        <v>-3.6625</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3264</v>
+        <v>1.2248</v>
       </c>
       <c r="J142" t="n">
-        <v>29.1808</v>
+        <v>26.9456</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2081</v>
+        <v>1.1529</v>
       </c>
       <c r="J143" t="n">
-        <v>26.5782</v>
+        <v>25.3638</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7211</v>
+        <v>0.8236</v>
       </c>
       <c r="J144" t="n">
-        <v>15.8642</v>
+        <v>18.1192</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6287</v>
+        <v>0.7341</v>
       </c>
       <c r="J145" t="n">
-        <v>13.8314</v>
+        <v>16.1502</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4656</v>
+        <v>0.5698</v>
       </c>
       <c r="J146" t="n">
-        <v>10.2432</v>
+        <v>12.5356</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6801</v>
+        <v>0.8713</v>
       </c>
       <c r="J147" t="n">
-        <v>14.9622</v>
+        <v>19.1686</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.72</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3563</v>
+        <v>-0.2761</v>
       </c>
       <c r="J148" t="n">
-        <v>-7.8386</v>
+        <v>-6.0742</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.51</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.6926</v>
+        <v>-0.4697</v>
       </c>
       <c r="J149" t="n">
-        <v>-15.2372</v>
+        <v>-10.3334</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.48</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.732</v>
+        <v>-0.4979</v>
       </c>
       <c r="J150" t="n">
-        <v>-16.104</v>
+        <v>-10.9538</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8821</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.4062</v>
+        <v>-13.4288</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9866</v>
+        <v>0.9717</v>
       </c>
       <c r="J152" t="n">
-        <v>26.6382</v>
+        <v>26.2359</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.586</v>
+        <v>0.5739</v>
       </c>
       <c r="J153" t="n">
-        <v>15.822</v>
+        <v>15.4953</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0815</v>
+        <v>0.1361</v>
       </c>
       <c r="J154" t="n">
-        <v>2.2005</v>
+        <v>3.6747</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0454</v>
+        <v>0.1015</v>
       </c>
       <c r="J155" t="n">
-        <v>1.2258</v>
+        <v>2.7405</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.02</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0068</v>
+        <v>0.0646</v>
       </c>
       <c r="J156" t="n">
-        <v>0.1836</v>
+        <v>1.7442</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.45</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7138</v>
+        <v>0.8828</v>
       </c>
       <c r="J157" t="n">
-        <v>19.2726</v>
+        <v>23.8356</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2023</v>
+        <v>0.2108</v>
       </c>
       <c r="J158" t="n">
-        <v>5.4621</v>
+        <v>5.6916</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0481</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.1114</v>
+        <v>-1.2987</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5158</v>
+        <v>-0.3335</v>
       </c>
       <c r="J160" t="n">
-        <v>-13.9266</v>
+        <v>-9.0045</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.3524</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.6286</v>
+        <v>-9.514799999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9506</v>
+        <v>0.9497</v>
       </c>
       <c r="J162" t="n">
-        <v>25.6662</v>
+        <v>25.6419</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9064</v>
+        <v>0.9073</v>
       </c>
       <c r="J163" t="n">
-        <v>24.4728</v>
+        <v>24.4971</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>16.6698</v>
+        <v>17.0235</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.05</v>
+        <v>0.1192</v>
       </c>
       <c r="J165" t="n">
-        <v>1.35</v>
+        <v>3.2184</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0648</v>
+        <v>0.0063</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.7496</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0518</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>1.3986</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.92</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0914</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.5461</v>
+        <v>-2.4678</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.302</v>
+        <v>-0.2077</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.154</v>
+        <v>-5.6079</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4476</v>
+        <v>-0.2943</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.0852</v>
+        <v>-7.9461</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.66</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5326</v>
+        <v>-0.3513</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.3802</v>
+        <v>-9.485099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2034/event_2034_evp_summary.xlsx
+++ b/database/event/2034/event_2034_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7932</v>
+        <v>8.117699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3045</v>
+        <v>2.4004</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8802</v>
+        <v>3.0711</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7932</v>
+        <v>8.117699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7805</v>
+        <v>2.694</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0127</v>
+        <v>5.4237</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3106</v>
+        <v>3.9943</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2413</v>
+        <v>2.1569</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0127</v>
+        <v>5.4237</v>
       </c>
       <c r="K2" t="n">
         <v>73</v>
@@ -529,7 +529,7 @@
         <v>132</v>
       </c>
       <c r="M2" t="n">
-        <v>7.254</v>
+        <v>7.5806</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6305</v>
+        <v>5.585</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6649</v>
+        <v>1.6515</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9039</v>
+        <v>1.9182</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6305</v>
+        <v>5.585</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5786</v>
+        <v>2.4932</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0519</v>
+        <v>3.0918</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5992</v>
+        <v>3.3317</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8714</v>
+        <v>1.7991</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0519</v>
+        <v>3.0918</v>
       </c>
       <c r="K3" t="n">
         <v>73</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>4.923299999999999</v>
+        <v>4.8909</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2989</v>
+        <v>4.4583</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2712</v>
+        <v>1.3183</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3027</v>
+        <v>1.4053</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2989</v>
+        <v>4.4583</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9425</v>
+        <v>2.9514</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3564</v>
+        <v>1.5069</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8814</v>
+        <v>4.8436</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5381</v>
+        <v>2.6155</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3564</v>
+        <v>1.5069</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -621,7 +621,7 @@
         <v>118</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8945</v>
+        <v>4.1224</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -630,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7852</v>
+        <v>3.7778</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1193</v>
+        <v>1.1171</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0708</v>
+        <v>1.0955</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7852</v>
+        <v>3.7778</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0775</v>
+        <v>2.4987</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7077</v>
+        <v>1.2791</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0775</v>
+        <v>3.3501</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0802</v>
+        <v>1.809</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7077</v>
+        <v>1.2791</v>
       </c>
       <c r="K5" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7879</v>
+        <v>3.0881</v>
       </c>
       <c r="N5" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6404</v>
+        <v>3.7331</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0765</v>
+        <v>1.1039</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0054</v>
+        <v>1.0752</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6404</v>
+        <v>3.7331</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5424</v>
+        <v>2.2738</v>
       </c>
       <c r="G6" t="n">
-        <v>1.098</v>
+        <v>1.4593</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4717</v>
+        <v>2.608</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8051</v>
+        <v>1.4083</v>
       </c>
       <c r="J6" t="n">
-        <v>1.098</v>
+        <v>1.4593</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -713,7 +713,7 @@
         <v>118</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9031</v>
+        <v>2.8676</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6066</v>
+        <v>3.6979</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0665</v>
+        <v>1.0935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9902</v>
+        <v>1.0592</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6066</v>
+        <v>3.6979</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3106</v>
+        <v>1.866</v>
       </c>
       <c r="G7" t="n">
-        <v>1.296</v>
+        <v>1.8319</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6547</v>
+        <v>1.866</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3803</v>
+        <v>1.0076</v>
       </c>
       <c r="J7" t="n">
-        <v>1.296</v>
+        <v>1.8319</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L7" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6763</v>
+        <v>2.8395</v>
       </c>
       <c r="N7" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4241</v>
+        <v>3.4169</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0125</v>
+        <v>1.0104</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9312</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4241</v>
+        <v>3.4169</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5828</v>
+        <v>2.3071</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8413</v>
+        <v>1.1098</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6138</v>
+        <v>2.7178</v>
       </c>
       <c r="I8" t="n">
-        <v>1.879</v>
+        <v>1.4676</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8413</v>
+        <v>1.1098</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7203</v>
+        <v>2.5774</v>
       </c>
       <c r="N8" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3559</v>
+        <v>3.3786</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9923</v>
+        <v>0.9991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.877</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3559</v>
+        <v>3.3786</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3894</v>
+        <v>2.4725</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9665</v>
+        <v>0.9061</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9326</v>
+        <v>3.2636</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5248</v>
+        <v>1.7623</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9665</v>
+        <v>0.9061</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L9" t="n">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4913</v>
+        <v>2.6684</v>
       </c>
       <c r="N9" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8325</v>
+        <v>2.8204</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8376</v>
+        <v>0.834</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6407</v>
+        <v>0.6597</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8325</v>
+        <v>2.8204</v>
       </c>
       <c r="F10" t="n">
-        <v>1.397</v>
+        <v>1.3454</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4355</v>
+        <v>1.475</v>
       </c>
       <c r="H10" t="n">
-        <v>1.397</v>
+        <v>1.3454</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7264</v>
+        <v>0.7265</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4355</v>
+        <v>1.475</v>
       </c>
       <c r="K10" t="n">
         <v>73</v>
@@ -897,7 +897,7 @@
         <v>132</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1619</v>
+        <v>2.2015</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4472</v>
+        <v>2.5039</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7236</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4668</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4472</v>
+        <v>2.5039</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6138</v>
+        <v>1.5776</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8334</v>
+        <v>0.9263</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6138</v>
+        <v>1.5776</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8391</v>
+        <v>0.8519</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8334</v>
+        <v>0.9263</v>
       </c>
       <c r="K11" t="n">
         <v>40</v>
@@ -943,7 +943,7 @@
         <v>118</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6725</v>
+        <v>1.7782</v>
       </c>
       <c r="N11" t="n">
         <v>158</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.079</v>
+        <v>2.2271</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6148</v>
+        <v>0.6586</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3006</v>
+        <v>0.3896</v>
       </c>
       <c r="E12" t="n">
-        <v>2.079</v>
+        <v>2.2271</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6546</v>
+        <v>-0.2737</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5756</v>
+        <v>2.5008</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8667</v>
+        <v>-0.2737</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0105</v>
+        <v>-0.1478</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5756</v>
+        <v>2.5008</v>
       </c>
       <c r="K12" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4349</v>
+        <v>2.353</v>
       </c>
       <c r="N12" t="n">
-        <v>133</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0257</v>
+        <v>1.9519</v>
       </c>
       <c r="C13" t="n">
-        <v>0.599</v>
+        <v>0.5772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2765</v>
+        <v>0.2643</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0257</v>
+        <v>1.9519</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4087</v>
+        <v>2.5592</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4344</v>
+        <v>-0.6073</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4087</v>
+        <v>3.5495</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2125</v>
+        <v>1.9167</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4344</v>
+        <v>-0.6073</v>
       </c>
       <c r="K13" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="L13" t="n">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2219</v>
+        <v>1.3094</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7139</v>
+        <v>1.5231</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5068</v>
+        <v>0.4504</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1357</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7139</v>
+        <v>1.5231</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0883</v>
+        <v>1.9287</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3744</v>
+        <v>-0.4056</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0883</v>
+        <v>1.9287</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0858</v>
+        <v>1.0415</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3744</v>
+        <v>-0.4056</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1081,7 +1081,7 @@
         <v>58</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7114</v>
+        <v>0.6359000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>112</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3318</v>
+        <v>0.3291</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1315</v>
+        <v>-0.1176</v>
       </c>
       <c r="E15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="F15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="I15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.122</v>
+        <v>1.1128</v>
       </c>
       <c r="N15" t="n">
         <v>89</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3203</v>
+        <v>0.3114</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.149</v>
+        <v>-0.1448</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0832</v>
+        <v>1.0531</v>
       </c>
       <c r="N16" t="n">
         <v>89</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0204</v>
+        <v>0.9356</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3017</v>
+        <v>0.2767</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1774</v>
+        <v>-0.1983</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0204</v>
+        <v>0.9356</v>
       </c>
       <c r="F17" t="n">
-        <v>1.333</v>
+        <v>1.2822</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3126</v>
+        <v>-0.3466</v>
       </c>
       <c r="H17" t="n">
-        <v>1.333</v>
+        <v>1.2822</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6931</v>
+        <v>0.6924</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3126</v>
+        <v>-0.3466</v>
       </c>
       <c r="K17" t="n">
         <v>54</v>
@@ -1219,7 +1219,7 @@
         <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3805000000000001</v>
+        <v>0.3458</v>
       </c>
       <c r="N17" t="n">
         <v>112</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0046</v>
+        <v>0.9084</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2971</v>
+        <v>0.2686</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1845</v>
+        <v>-0.2107</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0046</v>
+        <v>0.9084</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3368</v>
+        <v>1.2745</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3322</v>
+        <v>-0.3661</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3368</v>
+        <v>1.2745</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6882</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3322</v>
+        <v>-0.3661</v>
       </c>
       <c r="K18" t="n">
         <v>54</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3629000000000001</v>
+        <v>0.3221000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>112</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2318</v>
+        <v>0.2369</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2841</v>
+        <v>-0.2596</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7839</v>
+        <v>0.801</v>
       </c>
       <c r="N19" t="n">
         <v>89</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2201</v>
+        <v>0.2101</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3019</v>
+        <v>-0.3008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="N20" t="n">
         <v>73</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1996</v>
+        <v>0.1798</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3332</v>
+        <v>-0.3473</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6751</v>
+        <v>0.6082</v>
       </c>
       <c r="N21" t="n">
         <v>54</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1782</v>
+        <v>0.148</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.366</v>
+        <v>-0.3964</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6025</v>
+        <v>0.5004</v>
       </c>
       <c r="N22" t="n">
         <v>73</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3875</v>
+        <v>0.244</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1146</v>
+        <v>0.0722</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4631</v>
+        <v>-0.5131</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3875</v>
+        <v>0.244</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5802</v>
+        <v>0.463</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1927</v>
+        <v>-0.219</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5802</v>
+        <v>0.463</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3017</v>
+        <v>0.25</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1927</v>
+        <v>-0.219</v>
       </c>
       <c r="K23" t="n">
         <v>89</v>
@@ -1495,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.109</v>
+        <v>0.031</v>
       </c>
       <c r="N23" t="n">
         <v>133</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0117</v>
+        <v>-0.0185</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6559</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0397</v>
+        <v>-0.0625</v>
       </c>
       <c r="N24" t="n">
         <v>54</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0328</v>
+        <v>-0.0418</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6881</v>
+        <v>-0.6885</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.111</v>
+        <v>-0.1412</v>
       </c>
       <c r="N25" t="n">
         <v>73</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0415</v>
+        <v>-0.0442</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7014</v>
+        <v>-0.6923</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1405</v>
+        <v>-0.1496</v>
       </c>
       <c r="N26" t="n">
         <v>54</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1064</v>
+        <v>-0.1076</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8004</v>
+        <v>-0.7899</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3598</v>
+        <v>-0.3639</v>
       </c>
       <c r="N27" t="n">
         <v>89</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1181</v>
+        <v>-0.1233</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8184</v>
+        <v>-0.8141</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3995</v>
+        <v>-0.4171</v>
       </c>
       <c r="N28" t="n">
         <v>89</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1312</v>
+        <v>-0.1395</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8384</v>
+        <v>-0.839</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4438</v>
+        <v>-0.4719</v>
       </c>
       <c r="N29" t="n">
         <v>54</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1492</v>
+        <v>-0.1616</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8659</v>
+        <v>-0.8729</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5047</v>
+        <v>-0.5464</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1538</v>
+        <v>-0.1671</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8728</v>
+        <v>-0.8815</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.52</v>
+        <v>-0.5652</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1856</v>
+        <v>-0.1942</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9214</v>
+        <v>-0.9232</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6278</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>54</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>darti</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6968</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.199</v>
+        <v>-0.206</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9418</v>
+        <v>-0.9414</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6968</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2633</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.9601</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2633</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1422</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.9601</v>
       </c>
       <c r="K33" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.8179</v>
       </c>
       <c r="N33" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>darti</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7366</v>
+        <v>-0.71</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2178</v>
+        <v>-0.2099</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9706</v>
+        <v>-0.9474</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7366</v>
+        <v>-0.71</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2073</v>
+        <v>-0.71</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2073</v>
+        <v>-0.71</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1078</v>
+        <v>-0.71</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L34" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8361</v>
+        <v>-0.71</v>
       </c>
       <c r="N34" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>downie</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2226</v>
+        <v>-0.2303</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9779</v>
+        <v>-0.9787</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7528</v>
+        <v>-0.7788</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>downie</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2244</v>
+        <v>-0.2339</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9807</v>
+        <v>-0.9843</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.759</v>
+        <v>-0.791</v>
       </c>
       <c r="N36" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2265</v>
+        <v>-0.2362</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9839</v>
+        <v>-0.9878</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7661</v>
+        <v>-0.7987</v>
       </c>
       <c r="N37" t="n">
         <v>73</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2847</v>
+        <v>-0.2914</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0726</v>
+        <v>-1.0728</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9627</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>40</v>
@@ -2194,35 +2194,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SileNt</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2261</v>
+        <v>-1.2302</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3626</v>
+        <v>-0.3638</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1915</v>
+        <v>-1.1842</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2261</v>
+        <v>-1.2302</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4074</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6359</v>
+        <v>-0.8228</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4074</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3069</v>
+        <v>-0.22</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6359</v>
+        <v>-0.8228</v>
       </c>
       <c r="K39" t="n">
         <v>89</v>
@@ -2231,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9428000000000001</v>
+        <v>-1.0428</v>
       </c>
       <c r="N39" t="n">
         <v>133</v>
@@ -2240,35 +2240,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>SileNt</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2432</v>
+        <v>-1.2526</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3676</v>
+        <v>-0.3704</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1993</v>
+        <v>-1.1944</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2432</v>
+        <v>-1.2526</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4439</v>
+        <v>-0.5737</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7993</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4439</v>
+        <v>-0.5737</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2308</v>
+        <v>-0.3098</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7993</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="K40" t="n">
         <v>89</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0301</v>
+        <v>-0.9886999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>133</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8953</v>
+        <v>-1.8798</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5604</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4936</v>
+        <v>-1.4799</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8953</v>
+        <v>-1.8798</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1966</v>
+        <v>-1.1432</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6987</v>
+        <v>-0.7366</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1966</v>
+        <v>-1.1432</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6222</v>
+        <v>-0.6173</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6987</v>
+        <v>-0.7366</v>
       </c>
       <c r="K41" t="n">
         <v>89</v>
@@ -2323,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3209</v>
+        <v>-1.3539</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4015</v>
+        <v>1.5125</v>
       </c>
       <c r="J2" t="n">
-        <v>35.0375</v>
+        <v>37.8125</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0305</v>
+        <v>0.9862</v>
       </c>
       <c r="J3" t="n">
-        <v>25.7625</v>
+        <v>24.655</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6148</v>
+        <v>0.5979</v>
       </c>
       <c r="J4" t="n">
-        <v>15.37</v>
+        <v>14.9475</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3628</v>
+        <v>0.3707</v>
       </c>
       <c r="J5" t="n">
-        <v>9.07</v>
+        <v>9.2675</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2402</v>
+        <v>-0.2216</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.005</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2655</v>
+        <v>0.2567</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6375</v>
+        <v>6.4175</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0276</v>
+        <v>-0.0409</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.0225</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.77</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2467</v>
+        <v>-0.2646</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.1675</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.8475</v>
+        <v>-8.255000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4081</v>
+        <v>-0.4206</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2025</v>
+        <v>-10.515</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5125</v>
+        <v>0.5052</v>
       </c>
       <c r="J12" t="n">
-        <v>14.35</v>
+        <v>14.1456</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.419</v>
+        <v>0.4182</v>
       </c>
       <c r="J13" t="n">
-        <v>11.732</v>
+        <v>11.7096</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.89</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.145</v>
+        <v>-0.1581</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.06</v>
+        <v>-4.4268</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2587</v>
+        <v>-0.2719</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.2436</v>
+        <v>-7.6132</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3074</v>
+        <v>-0.3196</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.607200000000001</v>
+        <v>-8.9488</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3728</v>
+        <v>0.386</v>
       </c>
       <c r="J17" t="n">
-        <v>10.4384</v>
+        <v>10.808</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3608</v>
+        <v>0.3745</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1024</v>
+        <v>10.486</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2999</v>
+        <v>0.3155</v>
       </c>
       <c r="J19" t="n">
-        <v>8.3972</v>
+        <v>8.834</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0675</v>
+        <v>0.0813</v>
       </c>
       <c r="J20" t="n">
-        <v>1.89</v>
+        <v>2.2764</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1266</v>
+        <v>-0.1352</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.5448</v>
+        <v>-3.7856</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4664</v>
+        <v>1.5985</v>
       </c>
       <c r="J22" t="n">
-        <v>30.7944</v>
+        <v>33.5685</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0957</v>
+        <v>1.0856</v>
       </c>
       <c r="J23" t="n">
-        <v>23.0097</v>
+        <v>22.7976</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0609</v>
+        <v>1.0343</v>
       </c>
       <c r="J24" t="n">
-        <v>22.2789</v>
+        <v>21.7203</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8746</v>
+        <v>0.8343</v>
       </c>
       <c r="J25" t="n">
-        <v>18.3666</v>
+        <v>17.5203</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.22</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5536</v>
+        <v>0.5506</v>
       </c>
       <c r="J26" t="n">
-        <v>11.6256</v>
+        <v>11.5626</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.72</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2513</v>
+        <v>-0.278</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.2773</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.71</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2619</v>
+        <v>-0.2881</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.4999</v>
+        <v>-6.0501</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.52</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.442</v>
+        <v>-0.4592</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.282</v>
+        <v>-9.6432</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.48</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4795</v>
+        <v>-0.4943</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.0695</v>
+        <v>-10.3803</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4984</v>
+        <v>-0.5119</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.4664</v>
+        <v>-10.7499</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0308</v>
+        <v>1.1442</v>
       </c>
       <c r="J32" t="n">
-        <v>19.5852</v>
+        <v>21.7398</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.67</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0082</v>
+        <v>1.1201</v>
       </c>
       <c r="J33" t="n">
-        <v>19.1558</v>
+        <v>21.2819</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.65</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9856</v>
+        <v>1.0958</v>
       </c>
       <c r="J34" t="n">
-        <v>18.7264</v>
+        <v>20.8202</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.48</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7913</v>
+        <v>0.8853</v>
       </c>
       <c r="J35" t="n">
-        <v>15.0347</v>
+        <v>16.8207</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.34</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6162</v>
+        <v>0.6937</v>
       </c>
       <c r="J36" t="n">
-        <v>11.7078</v>
+        <v>13.1803</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.63</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3181</v>
+        <v>-0.3457</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.0439</v>
+        <v>-6.5683</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.55</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3999</v>
+        <v>-0.4223</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.5981</v>
+        <v>-8.0237</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.54</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4096</v>
+        <v>-0.4313</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.7824</v>
+        <v>-8.194699999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.45</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4908</v>
+        <v>-0.5074</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.325200000000001</v>
+        <v>-9.640599999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6179</v>
+        <v>-0.6239</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.7401</v>
+        <v>-11.8541</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7695</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>19.2375</v>
+        <v>21.3825</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.719</v>
+        <v>0.8003</v>
       </c>
       <c r="J43" t="n">
-        <v>17.975</v>
+        <v>20.0075</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7063</v>
+        <v>0.7865</v>
       </c>
       <c r="J44" t="n">
-        <v>17.6575</v>
+        <v>19.6625</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.3</v>
       </c>
       <c r="I45" t="n">
-        <v>0.592</v>
+        <v>0.6601</v>
       </c>
       <c r="J45" t="n">
-        <v>14.8</v>
+        <v>16.5025</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0209</v>
+        <v>0.0491</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5225</v>
+        <v>1.2275</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2072</v>
+        <v>0.2033</v>
       </c>
       <c r="J47" t="n">
-        <v>5.18</v>
+        <v>5.0825</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0848</v>
+        <v>-0.0999</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.12</v>
+        <v>-2.4975</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1814</v>
+        <v>-0.1989</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.535</v>
+        <v>-4.9725</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2891</v>
+        <v>-0.3053</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.2275</v>
+        <v>-7.6325</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3178</v>
+        <v>-0.3332</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.945</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3955</v>
+        <v>0.4248</v>
       </c>
       <c r="J52" t="n">
-        <v>11.865</v>
+        <v>12.744</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0911</v>
+        <v>-0.1047</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.733</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1347</v>
+        <v>-0.1501</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.041</v>
+        <v>-4.503</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1452</v>
+        <v>-0.1609</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.356</v>
+        <v>-4.827</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.62</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3994</v>
+        <v>-0.4106</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.982</v>
+        <v>-12.318</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9045</v>
+        <v>0.9966</v>
       </c>
       <c r="J57" t="n">
-        <v>27.135</v>
+        <v>29.898</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4669</v>
+        <v>0.5171</v>
       </c>
       <c r="J58" t="n">
-        <v>14.007</v>
+        <v>15.513</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4529</v>
+        <v>0.5012</v>
       </c>
       <c r="J59" t="n">
-        <v>13.587</v>
+        <v>15.036</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3787</v>
+        <v>0.4087</v>
       </c>
       <c r="J60" t="n">
-        <v>11.361</v>
+        <v>12.261</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1835</v>
+        <v>-0.1726</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.505</v>
+        <v>-5.178</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4458</v>
+        <v>0.4813</v>
       </c>
       <c r="J62" t="n">
-        <v>12.4824</v>
+        <v>13.4764</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1674</v>
+        <v>-0.1857</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.6872</v>
+        <v>-5.1996</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1975</v>
+        <v>-0.216</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.53</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2833</v>
+        <v>-0.3009</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.9324</v>
+        <v>-8.4252</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5445</v>
+        <v>-0.5495</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.246</v>
+        <v>-15.386</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7278</v>
+        <v>0.8109</v>
       </c>
       <c r="J67" t="n">
-        <v>20.3784</v>
+        <v>22.7052</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6526</v>
+        <v>0.7282</v>
       </c>
       <c r="J68" t="n">
-        <v>18.2728</v>
+        <v>20.3896</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6526</v>
+        <v>0.7282</v>
       </c>
       <c r="J69" t="n">
-        <v>18.2728</v>
+        <v>20.3896</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.34</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6403</v>
+        <v>0.7145</v>
       </c>
       <c r="J70" t="n">
-        <v>17.9284</v>
+        <v>20.006</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.24</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5084</v>
+        <v>0.5676</v>
       </c>
       <c r="J71" t="n">
-        <v>14.2352</v>
+        <v>15.8928</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5997</v>
+        <v>0.5785</v>
       </c>
       <c r="J72" t="n">
-        <v>17.3913</v>
+        <v>16.7765</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3587</v>
+        <v>0.3562</v>
       </c>
       <c r="J73" t="n">
-        <v>10.4023</v>
+        <v>10.3298</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.01</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0456</v>
+        <v>0.049</v>
       </c>
       <c r="J74" t="n">
-        <v>1.3224</v>
+        <v>1.421</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3311</v>
+        <v>-0.3437</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.601900000000001</v>
+        <v>-9.9673</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.64</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3875</v>
+        <v>-0.3981</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.2375</v>
+        <v>-11.5449</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3229</v>
+        <v>1.2925</v>
       </c>
       <c r="J77" t="n">
-        <v>38.3641</v>
+        <v>37.4825</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1748</v>
+        <v>0.185</v>
       </c>
       <c r="J78" t="n">
-        <v>5.0692</v>
+        <v>5.365</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1748</v>
+        <v>0.185</v>
       </c>
       <c r="J79" t="n">
-        <v>5.0692</v>
+        <v>5.365</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2898</v>
+        <v>-0.2803</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.404199999999999</v>
+        <v>-8.1287</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4082</v>
+        <v>-0.3896</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.8378</v>
+        <v>-11.2984</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.19</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1556</v>
+        <v>1.1621</v>
       </c>
       <c r="J82" t="n">
-        <v>21.9564</v>
+        <v>22.0799</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6394</v>
+        <v>0.6463</v>
       </c>
       <c r="J83" t="n">
-        <v>12.1486</v>
+        <v>12.2797</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.29</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3658</v>
+        <v>0.3858</v>
       </c>
       <c r="J84" t="n">
-        <v>6.9502</v>
+        <v>7.3302</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3426</v>
+        <v>0.3634</v>
       </c>
       <c r="J85" t="n">
-        <v>6.5094</v>
+        <v>6.9046</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.228</v>
+        <v>-0.2329</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.332</v>
+        <v>-4.4251</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0146</v>
+        <v>-0.0347</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.2774</v>
+        <v>-0.6593</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.91</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0801</v>
+        <v>-0.1022</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.5219</v>
+        <v>-1.9418</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3545</v>
+        <v>-0.3722</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.7355</v>
+        <v>-7.0718</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4292</v>
+        <v>-0.4433</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.1548</v>
+        <v>-8.422700000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.476</v>
+        <v>-0.4873</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.044</v>
+        <v>-9.258699999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.11</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2975</v>
+        <v>0.2944</v>
       </c>
       <c r="J92" t="n">
-        <v>12.1975</v>
+        <v>12.0704</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0594</v>
+        <v>0.059</v>
       </c>
       <c r="J93" t="n">
-        <v>2.4354</v>
+        <v>2.419</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1559</v>
+        <v>-0.1717</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.3919</v>
+        <v>-7.0397</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2171</v>
+        <v>-0.2332</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.9011</v>
+        <v>-9.561199999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3149</v>
+        <v>-0.3292</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.9109</v>
+        <v>-13.4972</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0675</v>
+        <v>1.0176</v>
       </c>
       <c r="J97" t="n">
-        <v>43.7675</v>
+        <v>41.7216</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7677</v>
+        <v>0.7264</v>
       </c>
       <c r="J98" t="n">
-        <v>31.4757</v>
+        <v>29.7824</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0236</v>
+        <v>0.0383</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9676</v>
+        <v>1.5703</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1272</v>
+        <v>-0.1226</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.2152</v>
+        <v>-5.0266</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1994</v>
+        <v>-0.193</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.1754</v>
+        <v>-7.913</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4446</v>
+        <v>1.4316</v>
       </c>
       <c r="J102" t="n">
-        <v>31.7812</v>
+        <v>31.4952</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.793</v>
+        <v>0.7571</v>
       </c>
       <c r="J103" t="n">
-        <v>17.446</v>
+        <v>16.6562</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7043</v>
+        <v>0.6783</v>
       </c>
       <c r="J104" t="n">
-        <v>15.4946</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3587</v>
+        <v>0.3678</v>
       </c>
       <c r="J105" t="n">
-        <v>7.8914</v>
+        <v>8.0916</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2471</v>
+        <v>0.2651</v>
       </c>
       <c r="J106" t="n">
-        <v>5.4362</v>
+        <v>5.8322</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.91</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0767</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>-1.6874</v>
+        <v>-2.189</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.82</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1798</v>
+        <v>-0.2023</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.9556</v>
+        <v>-4.4506</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.67</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3248</v>
+        <v>-0.3441</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.1456</v>
+        <v>-7.5702</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3341</v>
+        <v>-0.353</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.3502</v>
+        <v>-7.766</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5208</v>
+        <v>-0.5295</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.4576</v>
+        <v>-11.649</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>2.25</v>
       </c>
       <c r="I112" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J112" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.81</v>
       </c>
       <c r="I113" t="n">
-        <v>1.4464</v>
+        <v>1.4412</v>
       </c>
       <c r="J113" t="n">
-        <v>26.0352</v>
+        <v>25.9416</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7318</v>
+        <v>0.7105</v>
       </c>
       <c r="J114" t="n">
-        <v>13.1724</v>
+        <v>12.789</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.24</v>
       </c>
       <c r="I115" t="n">
-        <v>0.592</v>
+        <v>0.5868</v>
       </c>
       <c r="J115" t="n">
-        <v>10.656</v>
+        <v>10.5624</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0643</v>
+        <v>-0.0233</v>
       </c>
       <c r="J116" t="n">
-        <v>-1.1574</v>
+        <v>-0.4194</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0008</v>
+        <v>-0.0357</v>
       </c>
       <c r="J117" t="n">
-        <v>0.0144</v>
+        <v>-0.6425999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.53</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.428</v>
+        <v>-0.4469</v>
       </c>
       <c r="J118" t="n">
-        <v>-7.704</v>
+        <v>-8.0442</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.53</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.428</v>
+        <v>-0.4469</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.704</v>
+        <v>-8.0442</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4931</v>
+        <v>-0.5077</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.8758</v>
+        <v>-9.1386</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6286</v>
+        <v>-0.6324</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.3148</v>
+        <v>-11.3832</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2812</v>
+        <v>1.2511</v>
       </c>
       <c r="J122" t="n">
-        <v>33.3112</v>
+        <v>32.5286</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9218</v>
+        <v>0.8633</v>
       </c>
       <c r="J123" t="n">
-        <v>23.9668</v>
+        <v>22.4458</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6166</v>
+        <v>0.594</v>
       </c>
       <c r="J124" t="n">
-        <v>16.0316</v>
+        <v>15.444</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.3998</v>
+        <v>-2.2256</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.1057</v>
+        <v>-1.0034</v>
       </c>
       <c r="J126" t="n">
-        <v>-28.7482</v>
+        <v>-26.0884</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2208</v>
+        <v>0.2187</v>
       </c>
       <c r="J127" t="n">
-        <v>5.7408</v>
+        <v>5.6862</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0761</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.9786</v>
+        <v>-2.3374</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1223</v>
+        <v>-0.1379</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.1798</v>
+        <v>-3.5854</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2239</v>
+        <v>-0.2406</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.8214</v>
+        <v>-6.2556</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3495</v>
+        <v>-0.3632</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.087</v>
+        <v>-9.443199999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2489</v>
+        <v>0.2501</v>
       </c>
       <c r="J132" t="n">
-        <v>6.2225</v>
+        <v>6.2525</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.07</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1666</v>
+        <v>0.1695</v>
       </c>
       <c r="J133" t="n">
-        <v>4.165</v>
+        <v>4.2375</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1439</v>
+        <v>-0.1599</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.5975</v>
+        <v>-3.9975</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3316</v>
+        <v>-0.3458</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.645</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.66</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.36</v>
+        <v>-0.3731</v>
       </c>
       <c r="J136" t="n">
-        <v>-9</v>
+        <v>-9.327500000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7998</v>
+        <v>0.7891</v>
       </c>
       <c r="J137" t="n">
-        <v>19.995</v>
+        <v>19.7275</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.61</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7307</v>
       </c>
       <c r="J138" t="n">
-        <v>18.41</v>
+        <v>18.2675</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0725</v>
+        <v>-0.0757</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.8125</v>
+        <v>-1.8925</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0725</v>
+        <v>-0.0757</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.8125</v>
+        <v>-1.8925</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.91</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1465</v>
+        <v>-0.1537</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.6625</v>
+        <v>-3.8425</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2248</v>
+        <v>1.2014</v>
       </c>
       <c r="J142" t="n">
-        <v>26.9456</v>
+        <v>26.4308</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1529</v>
+        <v>1.1241</v>
       </c>
       <c r="J143" t="n">
-        <v>25.3638</v>
+        <v>24.7302</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8236</v>
+        <v>0.7867</v>
       </c>
       <c r="J144" t="n">
-        <v>18.1192</v>
+        <v>17.3074</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.7341</v>
+        <v>0.7079</v>
       </c>
       <c r="J145" t="n">
-        <v>16.1502</v>
+        <v>15.5738</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5698</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>12.5356</v>
+        <v>12.364</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8713</v>
+        <v>0.792</v>
       </c>
       <c r="J147" t="n">
-        <v>19.1686</v>
+        <v>17.424</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.72</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2761</v>
+        <v>-0.2973</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.0742</v>
+        <v>-6.5406</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.51</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4697</v>
+        <v>-0.4824</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.3334</v>
+        <v>-10.6128</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.48</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4979</v>
+        <v>-0.5087</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.9538</v>
+        <v>-11.1914</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6132</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.4288</v>
+        <v>-13.4904</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9717</v>
+        <v>0.9095</v>
       </c>
       <c r="J152" t="n">
-        <v>26.2359</v>
+        <v>24.5565</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5739</v>
+        <v>0.5546</v>
       </c>
       <c r="J153" t="n">
-        <v>15.4953</v>
+        <v>14.9742</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1361</v>
+        <v>0.1495</v>
       </c>
       <c r="J154" t="n">
-        <v>3.6747</v>
+        <v>4.0365</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1015</v>
+        <v>0.116</v>
       </c>
       <c r="J155" t="n">
-        <v>2.7405</v>
+        <v>3.132</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.02</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0646</v>
+        <v>0.0796</v>
       </c>
       <c r="J156" t="n">
-        <v>1.7442</v>
+        <v>2.1492</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.45</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8828</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>23.8356</v>
+        <v>22.5234</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2108</v>
+        <v>0.2167</v>
       </c>
       <c r="J158" t="n">
-        <v>5.6916</v>
+        <v>5.8509</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0481</v>
+        <v>-0.0567</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.2987</v>
+        <v>-1.5309</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3335</v>
+        <v>-0.3455</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.0045</v>
+        <v>-9.3285</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3524</v>
+        <v>-0.3638</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.514799999999999</v>
+        <v>-9.8226</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9497</v>
+        <v>0.892</v>
       </c>
       <c r="J162" t="n">
-        <v>25.6419</v>
+        <v>24.084</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9073</v>
+        <v>0.8528</v>
       </c>
       <c r="J163" t="n">
-        <v>24.4971</v>
+        <v>23.0256</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6086</v>
       </c>
       <c r="J164" t="n">
-        <v>17.0235</v>
+        <v>16.4322</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1192</v>
+        <v>0.1378</v>
       </c>
       <c r="J165" t="n">
-        <v>3.2184</v>
+        <v>3.7206</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0063</v>
+        <v>0.0262</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1701</v>
+        <v>0.7074</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="J167" t="n">
-        <v>0.2268</v>
+        <v>-0.1566</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.92</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0914</v>
+        <v>-0.1081</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.4678</v>
+        <v>-2.9187</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2077</v>
+        <v>-0.226</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.6079</v>
+        <v>-6.102</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2943</v>
+        <v>-0.3113</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.9461</v>
+        <v>-8.405099999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.66</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3513</v>
+        <v>-0.3663</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.485099999999999</v>
+        <v>-9.8901</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2034/event_2034_evp_summary.xlsx
+++ b/database/event/2034/event_2034_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.117699999999999</v>
+        <v>8.197800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4004</v>
+        <v>2.4241</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0711</v>
+        <v>3.1287</v>
       </c>
       <c r="E2" t="n">
-        <v>8.117699999999999</v>
+        <v>8.197800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.694</v>
+        <v>2.7284</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4237</v>
+        <v>5.4694</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9943</v>
+        <v>3.8009</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1569</v>
+        <v>2.1341</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4237</v>
+        <v>5.4694</v>
       </c>
       <c r="K2" t="n">
         <v>73</v>
@@ -529,7 +529,7 @@
         <v>132</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5806</v>
+        <v>7.6035</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.585</v>
+        <v>5.6648</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6515</v>
+        <v>1.6751</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9182</v>
+        <v>1.9748</v>
       </c>
       <c r="E3" t="n">
-        <v>5.585</v>
+        <v>5.6648</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4932</v>
+        <v>2.5772</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0918</v>
+        <v>3.0876</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3317</v>
+        <v>3.2335</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7991</v>
+        <v>1.8155</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0918</v>
+        <v>3.0876</v>
       </c>
       <c r="K3" t="n">
         <v>73</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8909</v>
+        <v>4.9031</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4583</v>
+        <v>4.4218</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3183</v>
+        <v>1.3075</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4053</v>
+        <v>1.4086</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4583</v>
+        <v>4.4218</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9514</v>
+        <v>2.9662</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5069</v>
+        <v>1.4556</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8436</v>
+        <v>4.6938</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6155</v>
+        <v>2.6354</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5069</v>
+        <v>1.4556</v>
       </c>
       <c r="K4" t="n">
         <v>40</v>
@@ -621,7 +621,7 @@
         <v>118</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1224</v>
+        <v>4.091</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7778</v>
+        <v>3.8418</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1171</v>
+        <v>1.136</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0955</v>
+        <v>1.1443</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7778</v>
+        <v>3.8418</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4987</v>
+        <v>2.3895</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2791</v>
+        <v>1.4523</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3501</v>
+        <v>2.5285</v>
       </c>
       <c r="I5" t="n">
-        <v>1.809</v>
+        <v>1.4197</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2791</v>
+        <v>1.4523</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -667,7 +667,7 @@
         <v>118</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0881</v>
+        <v>2.872</v>
       </c>
       <c r="N5" t="n">
         <v>158</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7331</v>
+        <v>3.7893</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1039</v>
+        <v>1.1205</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0752</v>
+        <v>1.1204</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7331</v>
+        <v>3.7893</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2738</v>
+        <v>2.5725</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4593</v>
+        <v>1.2168</v>
       </c>
       <c r="H6" t="n">
-        <v>2.608</v>
+        <v>3.2155</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4083</v>
+        <v>1.8054</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4593</v>
+        <v>1.2168</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -713,7 +713,7 @@
         <v>118</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8676</v>
+        <v>3.0222</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6979</v>
+        <v>3.5512</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0935</v>
+        <v>1.0501</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0592</v>
+        <v>1.012</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6979</v>
+        <v>3.5512</v>
       </c>
       <c r="F7" t="n">
-        <v>1.866</v>
+        <v>1.7274</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8319</v>
+        <v>1.8238</v>
       </c>
       <c r="H7" t="n">
-        <v>1.866</v>
+        <v>1.7274</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0076</v>
+        <v>0.9699</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8319</v>
+        <v>1.8238</v>
       </c>
       <c r="K7" t="n">
         <v>73</v>
@@ -759,7 +759,7 @@
         <v>132</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8395</v>
+        <v>2.7937</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4169</v>
+        <v>3.522</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0104</v>
+        <v>1.0415</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9312</v>
+        <v>0.9987</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4169</v>
+        <v>3.522</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3071</v>
+        <v>2.3939</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1098</v>
+        <v>1.1281</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7178</v>
+        <v>2.5451</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4676</v>
+        <v>1.429</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1098</v>
+        <v>1.1281</v>
       </c>
       <c r="K8" t="n">
         <v>40</v>
@@ -805,7 +805,7 @@
         <v>118</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5774</v>
+        <v>2.5571</v>
       </c>
       <c r="N8" t="n">
         <v>158</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3786</v>
+        <v>3.3525</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9991</v>
+        <v>0.9913</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9214</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3786</v>
+        <v>3.3525</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4725</v>
+        <v>2.534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9061</v>
+        <v>0.8185</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2636</v>
+        <v>3.0711</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7623</v>
+        <v>1.7243</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9061</v>
+        <v>0.8185</v>
       </c>
       <c r="K9" t="n">
         <v>54</v>
@@ -851,7 +851,7 @@
         <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6684</v>
+        <v>2.5428</v>
       </c>
       <c r="N9" t="n">
         <v>112</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8204</v>
+        <v>2.7324</v>
       </c>
       <c r="C10" t="n">
-        <v>0.834</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6597</v>
+        <v>0.639</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8204</v>
+        <v>2.7324</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3454</v>
+        <v>1.2587</v>
       </c>
       <c r="G10" t="n">
-        <v>1.475</v>
+        <v>1.4737</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3454</v>
+        <v>1.2587</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7265</v>
+        <v>0.7067</v>
       </c>
       <c r="J10" t="n">
-        <v>1.475</v>
+        <v>1.4737</v>
       </c>
       <c r="K10" t="n">
         <v>73</v>
@@ -897,7 +897,7 @@
         <v>132</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2015</v>
+        <v>2.1804</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5039</v>
+        <v>2.2467</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.6644</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4177</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5039</v>
+        <v>2.2467</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5776</v>
+        <v>-0.2086</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9263</v>
+        <v>2.4553</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5776</v>
+        <v>-0.2086</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8519</v>
+        <v>-0.1171</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9263</v>
+        <v>2.4553</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L11" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7782</v>
+        <v>2.3382</v>
       </c>
       <c r="N11" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2271</v>
+        <v>2.2222</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6586</v>
+        <v>0.6571</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3896</v>
+        <v>0.4065</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2271</v>
+        <v>2.2222</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2737</v>
+        <v>1.4177</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5008</v>
+        <v>0.8045</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2737</v>
+        <v>1.4177</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1478</v>
+        <v>0.796</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5008</v>
+        <v>0.8045</v>
       </c>
       <c r="K12" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="M12" t="n">
-        <v>2.353</v>
+        <v>1.6005</v>
       </c>
       <c r="N12" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9519</v>
+        <v>2.035</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5772</v>
+        <v>0.6018</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2643</v>
+        <v>0.3213</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9519</v>
+        <v>2.035</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5592</v>
+        <v>2.6289</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6073</v>
+        <v>-0.5939</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5495</v>
+        <v>3.4273</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9167</v>
+        <v>1.9243</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6073</v>
+        <v>-0.5939</v>
       </c>
       <c r="K13" t="n">
         <v>89</v>
@@ -1035,7 +1035,7 @@
         <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3094</v>
+        <v>1.3304</v>
       </c>
       <c r="N13" t="n">
         <v>133</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5231</v>
+        <v>1.406</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4504</v>
+        <v>0.4158</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0347</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5231</v>
+        <v>1.406</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9287</v>
+        <v>1.7793</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4056</v>
+        <v>-0.3733</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9287</v>
+        <v>1.7793</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0415</v>
+        <v>0.999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4056</v>
+        <v>-0.3733</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1081,7 +1081,7 @@
         <v>58</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6359000000000001</v>
+        <v>0.6256999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>112</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3291</v>
+        <v>0.307</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1176</v>
+        <v>-0.1329</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1128</v>
+        <v>1.0381</v>
       </c>
       <c r="N15" t="n">
         <v>89</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3114</v>
+        <v>0.2775</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1448</v>
+        <v>-0.1783</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0531</v>
+        <v>0.9383</v>
       </c>
       <c r="N16" t="n">
         <v>89</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9356</v>
+        <v>0.8127</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2767</v>
+        <v>0.2403</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1983</v>
+        <v>-0.2356</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9356</v>
+        <v>0.8127</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2822</v>
+        <v>1.124</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3466</v>
+        <v>-0.3113</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2822</v>
+        <v>1.124</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6924</v>
+        <v>0.6311</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3466</v>
+        <v>-0.3113</v>
       </c>
       <c r="K17" t="n">
         <v>54</v>
@@ -1219,7 +1219,7 @@
         <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3458</v>
+        <v>0.3198</v>
       </c>
       <c r="N17" t="n">
         <v>112</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9084</v>
+        <v>0.8065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2686</v>
+        <v>0.2385</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2107</v>
+        <v>-0.2384</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9084</v>
+        <v>0.8065</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2745</v>
+        <v>1.137</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3661</v>
+        <v>-0.3305</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2745</v>
+        <v>1.137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6882</v>
+        <v>0.6384</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3661</v>
+        <v>-0.3305</v>
       </c>
       <c r="K18" t="n">
         <v>54</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3221000000000001</v>
+        <v>0.3079</v>
       </c>
       <c r="N18" t="n">
         <v>112</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2369</v>
+        <v>0.1976</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2596</v>
+        <v>-0.3014</v>
       </c>
       <c r="E19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="F19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="I19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.801</v>
+        <v>0.6681</v>
       </c>
       <c r="N19" t="n">
         <v>89</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2101</v>
+        <v>0.1792</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3008</v>
+        <v>-0.3298</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7105</v>
+        <v>0.6059</v>
       </c>
       <c r="N20" t="n">
         <v>73</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1798</v>
+        <v>0.1699</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3473</v>
+        <v>-0.3441</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6082</v>
+        <v>0.5744</v>
       </c>
       <c r="N21" t="n">
         <v>54</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.148</v>
+        <v>0.1566</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3964</v>
+        <v>-0.3645</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5004</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>73</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.244</v>
+        <v>0.2662</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0722</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5131</v>
+        <v>-0.4845</v>
       </c>
       <c r="E23" t="n">
-        <v>0.244</v>
+        <v>0.2662</v>
       </c>
       <c r="F23" t="n">
-        <v>0.463</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.219</v>
+        <v>-0.2565</v>
       </c>
       <c r="H23" t="n">
-        <v>0.463</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.25</v>
+        <v>0.2935</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.219</v>
+        <v>-0.2565</v>
       </c>
       <c r="K23" t="n">
         <v>89</v>
@@ -1495,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.031</v>
+        <v>0.03699999999999998</v>
       </c>
       <c r="N23" t="n">
         <v>133</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0185</v>
+        <v>-0.0137</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.6269</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0625</v>
+        <v>-0.0463</v>
       </c>
       <c r="N24" t="n">
         <v>54</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>MoeycQ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0418</v>
+        <v>-0.0528</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6885</v>
+        <v>-0.6872</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1412</v>
+        <v>-0.1787</v>
       </c>
       <c r="N25" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MoeycQ</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0442</v>
+        <v>-0.0585</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6923</v>
+        <v>-0.696</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1496</v>
+        <v>-0.198</v>
       </c>
       <c r="N26" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1076</v>
+        <v>-0.1155</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7899</v>
+        <v>-0.7837</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3639</v>
+        <v>-0.3906</v>
       </c>
       <c r="N27" t="n">
         <v>89</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1233</v>
+        <v>-0.1175</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8141</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3973</v>
       </c>
       <c r="N28" t="n">
         <v>89</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1395</v>
+        <v>-0.1313</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.839</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4719</v>
+        <v>-0.4439</v>
       </c>
       <c r="N29" t="n">
         <v>54</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1616</v>
+        <v>-0.1556</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8729</v>
+        <v>-0.8455</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5464</v>
+        <v>-0.5263</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1671</v>
+        <v>-0.1581</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8815</v>
+        <v>-0.8494</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5652</v>
+        <v>-0.5347</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1942</v>
+        <v>-0.1847</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9232</v>
+        <v>-0.8904</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="N32" t="n">
         <v>54</v>
@@ -1918,124 +1918,124 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>darti</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6968</v>
+        <v>-0.6942</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.206</v>
+        <v>-0.2053</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9414</v>
+        <v>-0.922</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6968</v>
+        <v>-0.6942</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2633</v>
+        <v>-0.6942</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.9601</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2633</v>
+        <v>-0.6942</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1422</v>
+        <v>-0.6942</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9601</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L33" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8179</v>
+        <v>-0.6942</v>
       </c>
       <c r="N33" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>darti</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.71</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2099</v>
+        <v>-0.2243</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9474</v>
+        <v>-0.9514</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.71</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.71</v>
+        <v>0.1977</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.9563</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.71</v>
+        <v>0.1977</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.71</v>
+        <v>0.111</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.9563</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.71</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2303</v>
+        <v>-0.2251</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9787</v>
+        <v>-0.9526</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7614</v>
       </c>
       <c r="N35" t="n">
         <v>73</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>downie</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2339</v>
+        <v>-0.2264</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9843</v>
+        <v>-0.9546</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.791</v>
+        <v>-0.7657</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>downie</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2362</v>
+        <v>-0.2287</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9878</v>
+        <v>-0.9581</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7987</v>
+        <v>-0.7733</v>
       </c>
       <c r="N37" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2914</v>
+        <v>-0.2922</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0728</v>
+        <v>-1.056</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9883</v>
       </c>
       <c r="N38" t="n">
         <v>40</v>
@@ -2194,35 +2194,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>SileNt</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2302</v>
+        <v>-1.1861</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3638</v>
+        <v>-0.3507</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1842</v>
+        <v>-1.1461</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2302</v>
+        <v>-1.1861</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.4074</v>
+        <v>-0.5315</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8228</v>
+        <v>-0.6546</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4074</v>
+        <v>-0.5315</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.22</v>
+        <v>-0.2984</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8228</v>
+        <v>-0.6546</v>
       </c>
       <c r="K39" t="n">
         <v>89</v>
@@ -2231,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0428</v>
+        <v>-0.953</v>
       </c>
       <c r="N39" t="n">
         <v>133</v>
@@ -2240,35 +2240,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SileNt</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2526</v>
+        <v>-1.2655</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3704</v>
+        <v>-0.3742</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1944</v>
+        <v>-1.1823</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2526</v>
+        <v>-1.2655</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5737</v>
+        <v>-0.4472</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.8183</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5737</v>
+        <v>-0.4472</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3098</v>
+        <v>-0.2511</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.8183</v>
       </c>
       <c r="K40" t="n">
         <v>89</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9886999999999999</v>
+        <v>-1.0694</v>
       </c>
       <c r="N40" t="n">
         <v>133</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8798</v>
+        <v>-1.6555</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.4895</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4799</v>
+        <v>-1.3599</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8798</v>
+        <v>-1.6555</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1432</v>
+        <v>-0.9384</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7366</v>
+        <v>-0.7171</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1432</v>
+        <v>-0.9384</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6173</v>
+        <v>-0.5269</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7366</v>
+        <v>-0.7171</v>
       </c>
       <c r="K41" t="n">
         <v>89</v>
@@ -2323,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3539</v>
+        <v>-1.244</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5125</v>
+        <v>1.5447</v>
       </c>
       <c r="J2" t="n">
-        <v>37.8125</v>
+        <v>38.6175</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9862</v>
+        <v>0.9795</v>
       </c>
       <c r="J3" t="n">
-        <v>24.655</v>
+        <v>24.4875</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5979</v>
+        <v>0.5695</v>
       </c>
       <c r="J4" t="n">
-        <v>14.9475</v>
+        <v>14.2375</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3707</v>
+        <v>0.3385</v>
       </c>
       <c r="J5" t="n">
-        <v>9.2675</v>
+        <v>8.4625</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2216</v>
+        <v>-0.1889</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.54</v>
+        <v>-4.7225</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2567</v>
+        <v>0.2133</v>
       </c>
       <c r="J7" t="n">
-        <v>6.4175</v>
+        <v>5.3325</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0409</v>
+        <v>-0.0317</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0225</v>
+        <v>-0.7925</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.77</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2646</v>
+        <v>-0.2465</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.615</v>
+        <v>-6.1625</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.255000000000001</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4206</v>
+        <v>-0.4109</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.515</v>
+        <v>-10.2725</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5052</v>
+        <v>0.5161</v>
       </c>
       <c r="J12" t="n">
-        <v>14.1456</v>
+        <v>14.4508</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4182</v>
+        <v>0.4173</v>
       </c>
       <c r="J13" t="n">
-        <v>11.7096</v>
+        <v>11.6844</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.89</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1581</v>
+        <v>-0.1381</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.4268</v>
+        <v>-3.8668</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.78</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2719</v>
+        <v>-0.2527</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.6132</v>
+        <v>-7.0756</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3196</v>
+        <v>-0.3029</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.9488</v>
+        <v>-8.481199999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.386</v>
+        <v>0.3242</v>
       </c>
       <c r="J17" t="n">
-        <v>10.808</v>
+        <v>9.0776</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3745</v>
+        <v>0.3135</v>
       </c>
       <c r="J18" t="n">
-        <v>10.486</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3155</v>
+        <v>0.2598</v>
       </c>
       <c r="J19" t="n">
-        <v>8.834</v>
+        <v>7.2744</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0813</v>
+        <v>0.0596</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2764</v>
+        <v>1.6688</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1352</v>
+        <v>-0.1161</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7856</v>
+        <v>-3.2508</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5985</v>
+        <v>1.626</v>
       </c>
       <c r="J22" t="n">
-        <v>33.5685</v>
+        <v>34.146</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0856</v>
+        <v>1.0959</v>
       </c>
       <c r="J23" t="n">
-        <v>22.7976</v>
+        <v>23.0139</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0343</v>
+        <v>1.0401</v>
       </c>
       <c r="J24" t="n">
-        <v>21.7203</v>
+        <v>21.8421</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.36</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8343</v>
+        <v>0.8246</v>
       </c>
       <c r="J25" t="n">
-        <v>17.5203</v>
+        <v>17.3166</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.22</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5506</v>
+        <v>0.5238</v>
       </c>
       <c r="J26" t="n">
-        <v>11.5626</v>
+        <v>10.9998</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.72</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.278</v>
+        <v>-0.2654</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.838</v>
+        <v>-5.5734</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.71</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2881</v>
+        <v>-0.2762</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.0501</v>
+        <v>-5.8002</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.52</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4592</v>
+        <v>-0.4546</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.6432</v>
+        <v>-9.5466</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.48</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4943</v>
+        <v>-0.4922</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.3803</v>
+        <v>-10.3362</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5119</v>
+        <v>-0.5115</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.7499</v>
+        <v>-10.7415</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1442</v>
+        <v>1.1417</v>
       </c>
       <c r="J32" t="n">
-        <v>21.7398</v>
+        <v>21.6923</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.67</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1201</v>
+        <v>1.1168</v>
       </c>
       <c r="J33" t="n">
-        <v>21.2819</v>
+        <v>21.2192</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.65</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0958</v>
+        <v>1.092</v>
       </c>
       <c r="J34" t="n">
-        <v>20.8202</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.48</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8853</v>
+        <v>0.8797</v>
       </c>
       <c r="J35" t="n">
-        <v>16.8207</v>
+        <v>16.7143</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.34</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6937</v>
+        <v>0.6894</v>
       </c>
       <c r="J36" t="n">
-        <v>13.1803</v>
+        <v>13.0986</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.63</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3457</v>
+        <v>-0.3376</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.5683</v>
+        <v>-6.4144</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.55</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4223</v>
+        <v>-0.4198</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.0237</v>
+        <v>-7.9762</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.54</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4313</v>
+        <v>-0.4293</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.194699999999999</v>
+        <v>-8.156700000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.45</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5074</v>
+        <v>-0.5081</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.640599999999999</v>
+        <v>-9.6539</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6239</v>
+        <v>-0.6379</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.8541</v>
+        <v>-12.1201</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8418</v>
       </c>
       <c r="J42" t="n">
-        <v>21.3825</v>
+        <v>21.045</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8003</v>
+        <v>0.7874</v>
       </c>
       <c r="J43" t="n">
-        <v>20.0075</v>
+        <v>19.685</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7865</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>19.6625</v>
+        <v>19.3425</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.3</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6601</v>
+        <v>0.6513</v>
       </c>
       <c r="J45" t="n">
-        <v>16.5025</v>
+        <v>16.2825</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0491</v>
+        <v>0.0322</v>
       </c>
       <c r="J46" t="n">
-        <v>1.2275</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2033</v>
+        <v>0.1633</v>
       </c>
       <c r="J47" t="n">
-        <v>5.0825</v>
+        <v>4.0825</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0999</v>
+        <v>-0.0858</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.4975</v>
+        <v>-2.145</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1989</v>
+        <v>-0.1804</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.9725</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3053</v>
+        <v>-0.2878</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.6325</v>
+        <v>-7.195</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3332</v>
+        <v>-0.317</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.33</v>
+        <v>-7.925</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4248</v>
+        <v>0.3711</v>
       </c>
       <c r="J52" t="n">
-        <v>12.744</v>
+        <v>11.133</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1047</v>
+        <v>-0.0896</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.141</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1501</v>
+        <v>-0.1321</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.503</v>
+        <v>-3.963</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1609</v>
+        <v>-0.1424</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.827</v>
+        <v>-4.272</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.62</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4106</v>
+        <v>-0.4005</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.318</v>
+        <v>-12.015</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.53</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9966</v>
+        <v>0.984</v>
       </c>
       <c r="J57" t="n">
-        <v>29.898</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5171</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>15.513</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5012</v>
+        <v>0.4881</v>
       </c>
       <c r="J59" t="n">
-        <v>15.036</v>
+        <v>14.643</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4087</v>
+        <v>0.3748</v>
       </c>
       <c r="J60" t="n">
-        <v>12.261</v>
+        <v>11.244</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1726</v>
+        <v>-0.1413</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.178</v>
+        <v>-4.239</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4813</v>
+        <v>0.4474</v>
       </c>
       <c r="J62" t="n">
-        <v>13.4764</v>
+        <v>12.5272</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1857</v>
+        <v>-0.1689</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.1996</v>
+        <v>-4.7292</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.216</v>
+        <v>-0.1984</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.048</v>
+        <v>-5.5552</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3009</v>
+        <v>-0.2837</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.4252</v>
+        <v>-7.9436</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5495</v>
+        <v>-0.5558</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.386</v>
+        <v>-15.5624</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8109</v>
+        <v>0.7986</v>
       </c>
       <c r="J67" t="n">
-        <v>22.7052</v>
+        <v>22.3608</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7282</v>
+        <v>0.718</v>
       </c>
       <c r="J68" t="n">
-        <v>20.3896</v>
+        <v>20.104</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7282</v>
+        <v>0.718</v>
       </c>
       <c r="J69" t="n">
-        <v>20.3896</v>
+        <v>20.104</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.34</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7145</v>
+        <v>0.7046</v>
       </c>
       <c r="J70" t="n">
-        <v>20.006</v>
+        <v>19.7288</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.24</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5676</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>15.8928</v>
+        <v>15.792</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.28</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5785</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>16.7765</v>
+        <v>15.1003</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3562</v>
+        <v>0.3021</v>
       </c>
       <c r="J73" t="n">
-        <v>10.3298</v>
+        <v>8.760899999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.01</v>
       </c>
       <c r="I74" t="n">
-        <v>0.049</v>
+        <v>0.0328</v>
       </c>
       <c r="J74" t="n">
-        <v>1.421</v>
+        <v>0.9512</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3437</v>
+        <v>-0.3283</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.9673</v>
+        <v>-9.5207</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.64</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3981</v>
+        <v>-0.3872</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.5449</v>
+        <v>-11.2288</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2925</v>
+        <v>1.3155</v>
       </c>
       <c r="J77" t="n">
-        <v>37.4825</v>
+        <v>38.1495</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.185</v>
+        <v>0.1566</v>
       </c>
       <c r="J78" t="n">
-        <v>5.365</v>
+        <v>4.5414</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.05</v>
       </c>
       <c r="I79" t="n">
-        <v>0.185</v>
+        <v>0.1566</v>
       </c>
       <c r="J79" t="n">
-        <v>5.365</v>
+        <v>4.5414</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2803</v>
+        <v>-0.24</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.1287</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3896</v>
+        <v>-0.3469</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.2984</v>
+        <v>-10.0601</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.19</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1621</v>
+        <v>1.1287</v>
       </c>
       <c r="J82" t="n">
-        <v>22.0799</v>
+        <v>21.4453</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6463</v>
+        <v>0.5768</v>
       </c>
       <c r="J83" t="n">
-        <v>12.2797</v>
+        <v>10.9592</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.29</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3858</v>
+        <v>0.33</v>
       </c>
       <c r="J84" t="n">
-        <v>7.3302</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3634</v>
+        <v>0.3092</v>
       </c>
       <c r="J85" t="n">
-        <v>6.9046</v>
+        <v>5.8748</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2329</v>
+        <v>-0.2167</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.4251</v>
+        <v>-4.1173</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0347</v>
+        <v>-0.0216</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.6593</v>
+        <v>-0.4104</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.91</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1022</v>
+        <v>-0.0867</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.9418</v>
+        <v>-1.6473</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3722</v>
+        <v>-0.3595</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.0718</v>
+        <v>-6.8305</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4433</v>
+        <v>-0.4356</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.422700000000001</v>
+        <v>-8.276400000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4873</v>
+        <v>-0.4841</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.258699999999999</v>
+        <v>-9.197900000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.11</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2944</v>
+        <v>0.2449</v>
       </c>
       <c r="J92" t="n">
-        <v>12.0704</v>
+        <v>10.0409</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.059</v>
+        <v>0.0407</v>
       </c>
       <c r="J93" t="n">
-        <v>2.419</v>
+        <v>1.6687</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.87</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1717</v>
+        <v>-0.1527</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.0397</v>
+        <v>-6.2607</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2332</v>
+        <v>-0.2134</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.561199999999999</v>
+        <v>-8.7494</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3292</v>
+        <v>-0.3126</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.4972</v>
+        <v>-12.8166</v>
       </c>
     </row>
     <row r="97">
@@ -6269,10 +6269,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7264</v>
+        <v>0.6955</v>
       </c>
       <c r="J98" t="n">
-        <v>29.7824</v>
+        <v>28.5155</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0383</v>
+        <v>0.0279</v>
       </c>
       <c r="J99" t="n">
-        <v>1.5703</v>
+        <v>1.1439</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1226</v>
+        <v>-0.0955</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.0266</v>
+        <v>-3.9155</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.193</v>
+        <v>-0.1584</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.913</v>
+        <v>-6.4944</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4316</v>
+        <v>1.4589</v>
       </c>
       <c r="J102" t="n">
-        <v>31.4952</v>
+        <v>32.0958</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7571</v>
+        <v>0.7358</v>
       </c>
       <c r="J103" t="n">
-        <v>16.6562</v>
+        <v>16.1876</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6783</v>
+        <v>0.6536</v>
       </c>
       <c r="J104" t="n">
-        <v>14.9226</v>
+        <v>14.3792</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3678</v>
+        <v>0.3358</v>
       </c>
       <c r="J105" t="n">
-        <v>8.0916</v>
+        <v>7.3876</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.09</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2651</v>
+        <v>0.2341</v>
       </c>
       <c r="J106" t="n">
-        <v>5.8322</v>
+        <v>5.1502</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.91</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0837</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.189</v>
+        <v>-1.8414</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.82</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2023</v>
+        <v>-0.187</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.4506</v>
+        <v>-4.114</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.67</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3441</v>
+        <v>-0.3307</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.5702</v>
+        <v>-7.2754</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.353</v>
+        <v>-0.3398</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.766</v>
+        <v>-7.4756</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5295</v>
+        <v>-0.5315</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.649</v>
+        <v>-11.693</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>2.25</v>
       </c>
       <c r="I112" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J112" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.81</v>
       </c>
       <c r="I113" t="n">
-        <v>1.4412</v>
+        <v>1.4696</v>
       </c>
       <c r="J113" t="n">
-        <v>25.9416</v>
+        <v>26.4528</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7105</v>
+        <v>0.6932</v>
       </c>
       <c r="J114" t="n">
-        <v>12.789</v>
+        <v>12.4776</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.24</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5868</v>
+        <v>0.5619</v>
       </c>
       <c r="J115" t="n">
-        <v>10.5624</v>
+        <v>10.1142</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0233</v>
+        <v>-0.0392</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.4194</v>
+        <v>-0.7056</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.92</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0357</v>
+        <v>-0.0032</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.0576</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.53</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.4469</v>
+        <v>-0.4426</v>
       </c>
       <c r="J118" t="n">
-        <v>-8.0442</v>
+        <v>-7.9668</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.53</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4469</v>
+        <v>-0.4426</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.0442</v>
+        <v>-7.9668</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.46</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5077</v>
+        <v>-0.5072</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.1386</v>
+        <v>-9.1296</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.32</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6324</v>
+        <v>-0.6485</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.3832</v>
+        <v>-11.673</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2511</v>
+        <v>1.2697</v>
       </c>
       <c r="J122" t="n">
-        <v>32.5286</v>
+        <v>33.0122</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8633</v>
+        <v>0.8423</v>
       </c>
       <c r="J123" t="n">
-        <v>22.4458</v>
+        <v>21.8998</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.594</v>
+        <v>0.5585</v>
       </c>
       <c r="J124" t="n">
-        <v>15.444</v>
+        <v>14.521</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0856</v>
+        <v>-0.0646</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.2256</v>
+        <v>-1.6796</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0034</v>
+        <v>-1.0045</v>
       </c>
       <c r="J126" t="n">
-        <v>-26.0884</v>
+        <v>-26.117</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2187</v>
+        <v>0.1762</v>
       </c>
       <c r="J127" t="n">
-        <v>5.6862</v>
+        <v>4.5812</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.3374</v>
+        <v>-1.9838</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1379</v>
+        <v>-0.1211</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.5854</v>
+        <v>-3.1486</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2406</v>
+        <v>-0.2213</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.2556</v>
+        <v>-5.7538</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3632</v>
+        <v>-0.3489</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.443199999999999</v>
+        <v>-9.071400000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2501</v>
+        <v>0.2363</v>
       </c>
       <c r="J132" t="n">
-        <v>6.2525</v>
+        <v>5.9075</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.07</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1695</v>
+        <v>0.1529</v>
       </c>
       <c r="J133" t="n">
-        <v>4.2375</v>
+        <v>3.8225</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1599</v>
+        <v>-0.1419</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.9975</v>
+        <v>-3.5475</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3458</v>
+        <v>-0.3303</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.645</v>
+        <v>-8.2575</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.66</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3731</v>
+        <v>-0.3596</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.327500000000001</v>
+        <v>-8.99</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7891</v>
+        <v>0.7181</v>
       </c>
       <c r="J137" t="n">
-        <v>19.7275</v>
+        <v>17.9525</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.61</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7307</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>18.2675</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0757</v>
+        <v>-0.0615</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.8925</v>
+        <v>-1.5375</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0757</v>
+        <v>-0.0615</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.8925</v>
+        <v>-1.5375</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.91</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1537</v>
+        <v>-0.1347</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.8425</v>
+        <v>-3.3675</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2014</v>
+        <v>1.2177</v>
       </c>
       <c r="J142" t="n">
-        <v>26.4308</v>
+        <v>26.7894</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1241</v>
+        <v>1.1389</v>
       </c>
       <c r="J143" t="n">
-        <v>24.7302</v>
+        <v>25.0558</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7867</v>
+        <v>0.771</v>
       </c>
       <c r="J144" t="n">
-        <v>17.3074</v>
+        <v>16.962</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.7079</v>
+        <v>0.6877</v>
       </c>
       <c r="J145" t="n">
-        <v>15.5738</v>
+        <v>15.1294</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="J146" t="n">
-        <v>12.364</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I147" t="n">
-        <v>0.792</v>
+        <v>0.7892</v>
       </c>
       <c r="J147" t="n">
-        <v>17.424</v>
+        <v>17.3624</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.72</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2973</v>
+        <v>-0.2842</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.5406</v>
+        <v>-6.2524</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.51</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4824</v>
+        <v>-0.4786</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.6128</v>
+        <v>-10.5292</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.48</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5087</v>
+        <v>-0.5079</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.1914</v>
+        <v>-11.1738</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6132</v>
+        <v>-0.6279</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.4904</v>
+        <v>-13.8138</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9095</v>
+        <v>0.8923</v>
       </c>
       <c r="J152" t="n">
-        <v>24.5565</v>
+        <v>24.0921</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5546</v>
+        <v>0.517</v>
       </c>
       <c r="J153" t="n">
-        <v>14.9742</v>
+        <v>13.959</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1495</v>
+        <v>0.1247</v>
       </c>
       <c r="J154" t="n">
-        <v>4.0365</v>
+        <v>3.3669</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.116</v>
+        <v>0.0946</v>
       </c>
       <c r="J155" t="n">
-        <v>3.132</v>
+        <v>2.5542</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.02</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0796</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>2.1492</v>
+        <v>1.6929</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.45</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7864</v>
       </c>
       <c r="J157" t="n">
-        <v>22.5234</v>
+        <v>21.2328</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2167</v>
+        <v>0.1735</v>
       </c>
       <c r="J158" t="n">
-        <v>5.8509</v>
+        <v>4.6845</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0567</v>
+        <v>-0.0449</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.5309</v>
+        <v>-1.2123</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3455</v>
+        <v>-0.3304</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.3285</v>
+        <v>-8.9208</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3638</v>
+        <v>-0.3501</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.8226</v>
+        <v>-9.4527</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.892</v>
+        <v>0.8743</v>
       </c>
       <c r="J162" t="n">
-        <v>24.084</v>
+        <v>23.6061</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8528</v>
+        <v>0.832</v>
       </c>
       <c r="J163" t="n">
-        <v>23.0256</v>
+        <v>22.464</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.23</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6086</v>
+        <v>0.5757</v>
       </c>
       <c r="J164" t="n">
-        <v>16.4322</v>
+        <v>15.5439</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1378</v>
+        <v>0.1141</v>
       </c>
       <c r="J165" t="n">
-        <v>3.7206</v>
+        <v>3.0807</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0262</v>
+        <v>0.0164</v>
       </c>
       <c r="J166" t="n">
-        <v>0.7074</v>
+        <v>0.4428</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0058</v>
+        <v>-0.0014</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.1566</v>
+        <v>-0.0378</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.92</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1081</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.9187</v>
+        <v>-2.5326</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.226</v>
+        <v>-0.208</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.102</v>
+        <v>-5.616</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3113</v>
+        <v>-0.2943</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.405099999999999</v>
+        <v>-7.9461</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.66</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3663</v>
+        <v>-0.3522</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.8901</v>
+        <v>-9.509399999999999</v>
       </c>
     </row>
   </sheetData>
